--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Documents\GitHub\najlepsze-polskie-riffy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B717EE4-5E28-42A3-83AE-A9C03EF1200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B116BBE-C6BC-436A-B0FA-7C523155C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="366">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -101,6 +101,9 @@
     <t>Cykady na Cykladach</t>
   </si>
   <si>
+    <t>Kocham Cię Kochanie Moje</t>
+  </si>
+  <si>
     <t>Szerokie Wody</t>
   </si>
   <si>
@@ -419,6 +422,9 @@
     <t>Nie Rób Tyle Hałasu</t>
   </si>
   <si>
+    <t>Nie Wierz Nigdy Kobiecie</t>
+  </si>
+  <si>
     <t>Nie Wierze Skurwysynom</t>
   </si>
   <si>
@@ -734,6 +740,9 @@
     <t>https://drive.google.com/open?id=1Wh3pO4TudkMEYQbNVbz6Wcsr3cOUzZXw&amp;usp=drive_fs</t>
   </si>
   <si>
+    <t>https://drive.google.com/open?id=11WCSb6eFDj9y_ncnph1A661E-XQOlFbm&amp;usp=drive_fs</t>
+  </si>
+  <si>
     <t>https://drive.google.com/open?id=1kVLYxtinzKOjbVu3grZq5MhIzG8NU_x5&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -800,6 +809,9 @@
     <t>https://drive.google.com/open?id=1XzLQcWxwTvejIrh_EIzbn6AQj5Pj-bWO&amp;usp=drive_fs</t>
   </si>
   <si>
+    <t>https://drive.google.com/open?id=1Y1qnDr8VEL7NdVeWJr8xZUC8NMiEGLKX&amp;usp=drive_fs</t>
+  </si>
+  <si>
     <t>https://drive.google.com/open?id=1Y8FEumGobwIGDAmg6iAlq6CDnjwk16P5&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1097,52 +1109,28 @@
     <t xml:space="preserve">Bardzo szybki riff zbudowany w oparciu o tak zwany galop kostkowaniem naprzemiennym. Uwaga na zagrywkę na końcu, która pokonała niejednego gitarzystę. </t>
   </si>
   <si>
-    <t xml:space="preserve">To bardzo fajnie ułożone akordy w wyższych pozycjach, które należy ograć kostkowaniem. Akordy pochodzą z tak zwanego systemu Caged. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Ten riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
   </si>
   <si>
+    <t>Ale Wkoło Jest Wesoło (A)</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło (B)</t>
+  </si>
+  <si>
+    <t>To bardzo fajnie ułożone akordy w wyższych pozycjach, które należy ograć kostkowaniem. Akordy pochodzą z tak zwanego systemu Caged. Trzy gitary.</t>
+  </si>
+  <si>
     <t>Kiedy  Powiem Sobie Dość [RIFF A]</t>
   </si>
   <si>
-    <t>Kiedy  Powiem Sobie Dość [RIFF B]</t>
+    <t>Kiedy powiem sobie dość [RIFF B]</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1ccoFD7pBav79wTMOSp90IJfPt6mylrTs&amp;usp=drive_fs</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1WpbZBQufVbwuAsHTqMtoeCTQy3k52ws8&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>Kocham Cię Kochanie Moje [RIFF A]</t>
-  </si>
-  <si>
-    <t>Kocham Cię Kochanie Moje [RIFF B]</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=17KgN01ggjbpoJZXCvq9CJ0Bn702pUTWj&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=12vfZrots2a5LTsdPhLIEy3P2pFdubfyW&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>Nie wierz nigdy kobiecie [RIFF A]</t>
-  </si>
-  <si>
-    <t>Nie wierz nigdy kobiecie [RIFF B]</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło [RIFF A]</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło [RIFF B]</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1sKBxm895nh5IXUMIi0X5fuq8WUQYWZSm&amp;usp=drive_fs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=11kwrZ0SeedmPFjIAR_jEHO1sDAN7Ff5G&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1221,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1252,6 +1240,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1454,10 +1445,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:G131" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
-  <autoFilter ref="A1:G131" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G131">
-    <sortCondition ref="A1:A131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:G129" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
+  <autoFilter ref="A1:G129" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G129">
+    <sortCondition ref="A1:A129"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6FF1AA77-FAFD-461A-9D1E-E1F2F29A966E}" uniqueName="tytul" name="UTWÓR" dataDxfId="6">
@@ -1795,13 +1786,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="68.140625" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
@@ -1809,71 +1800,71 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1881,42 +1872,42 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G5" s="8"/>
     </row>
@@ -1925,137 +1916,137 @@
         <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2063,91 +2054,91 @@
         <v>0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2155,110 +2146,110 @@
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2266,271 +2257,271 @@
         <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="8" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="8"/>
@@ -2540,132 +2531,132 @@
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="8"/>
@@ -2675,73 +2666,73 @@
         <v>4</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="8"/>
@@ -2751,304 +2742,304 @@
         <v>2</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>358</v>
+        <v>45</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>359</v>
+        <v>43</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>365</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
-        <v>360</v>
+      <c r="A52" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>362</v>
+        <v>235</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>361</v>
+        <v>105</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>363</v>
+        <v>236</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="8"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>234</v>
+        <v>43</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="8"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>235</v>
+        <v>43</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F59" s="4"/>
-      <c r="G59" s="8"/>
+      <c r="G59" s="8" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F60" s="4"/>
-      <c r="G60" s="8" t="s">
-        <v>338</v>
-      </c>
+      <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>311</v>
@@ -3058,510 +3049,510 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>242</v>
+        <v>43</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="8"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>243</v>
+        <v>43</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="8"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="8"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>245</v>
+        <v>45</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>246</v>
+        <v>43</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="8"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="8"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="8"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="8"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="8"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="8"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="8"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="8"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>364</v>
+      <c r="A76" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>368</v>
+        <v>259</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="8"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>365</v>
+        <v>29</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>369</v>
+        <v>260</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="8"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="8"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="8"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="8"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="8"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="8"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="8"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="8"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>311</v>
@@ -3571,817 +3562,781 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>42</v>
+        <v>149</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>323</v>
+        <v>48</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="8"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="8"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>324</v>
+        <v>159</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="8"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="8"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="8"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="8"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>280</v>
+        <v>45</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="8"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="8"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>282</v>
+        <v>43</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="8"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="8"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="8"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="8"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="8"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>325</v>
+        <v>167</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="8"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="8"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="8"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="8"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="8"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="8"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="8"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="8"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>44</v>
+        <v>177</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="8"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="8"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>322</v>
+        <v>159</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="8"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="8"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="8"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="8"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="8"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F125" s="4"/>
-      <c r="G125" s="8"/>
+      <c r="G125" s="8" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="8"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>311</v>
       </c>
       <c r="F127" s="4"/>
-      <c r="G127" s="8" t="s">
-        <v>315</v>
-      </c>
+      <c r="G127" s="8"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>308</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="1"/>
       <c r="F128" s="4"/>
       <c r="G128" s="8"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>307</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="1"/>
       <c r="F129" s="4"/>
       <c r="G129" s="8"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="8"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="8"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C120" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
-    <hyperlink ref="C92" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
-    <hyperlink ref="C99" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
-    <hyperlink ref="C110" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
+    <hyperlink ref="C118" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
+    <hyperlink ref="C90" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
+    <hyperlink ref="C97" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
+    <hyperlink ref="C108" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
     <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{A1484470-F758-427A-8BC6-ADB24E480B76}"/>
     <hyperlink ref="D7" r:id="rId8" xr:uid="{422A23FB-E927-44A1-8543-D05FC652092F}"/>
+    <hyperlink ref="D49" r:id="rId9" xr:uid="{F029A23A-17F5-4A68-AF01-1C649484A988}"/>
+    <hyperlink ref="D50" r:id="rId10" xr:uid="{F745F40D-6EA2-40FD-A06B-A490C9F706EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2E0526-223F-4DB8-8176-4D8068E5E068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEB1F70-8E0A-4C71-AD72-BA8CDFE04447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -1115,12 +1115,6 @@
     <t>https://drive.google.com/open?id=12vfZrots2a5LTsdPhLIEy3P2pFdubfyW&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>Ale Wkoło Jest Wesoło [RIFF A]</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło [RIFF B]</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1sKBxm895nh5IXUMIi0X5fuq8WUQYWZSm&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1140,6 +1134,12 @@
   </si>
   <si>
     <t>Nie wierz nigdy kobiecie RIFF A</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło RIFF A</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło RIFF B</t>
   </si>
 </sst>
 </file>
@@ -1263,73 +1263,6 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1395,6 +1328,73 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1485,16 +1485,16 @@
     <tableColumn id="1" xr3:uid="{6FF1AA77-FAFD-461A-9D1E-E1F2F29A966E}" uniqueName="tytul" name="UTWÓR" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/utwory/utwor/tytul" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A8C8BEAA-52D6-4B99-A993-AEB7BDFB4843}" uniqueName="wykonawca" name="WYKONAWCA" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{A8C8BEAA-52D6-4B99-A993-AEB7BDFB4843}" uniqueName="wykonawca" name="WYKONAWCA" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/utwory/utwor/wykonawca" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FF58B829-2735-43FA-ABA3-887BEE564628}" uniqueName="youtube" name="YT" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{FF58B829-2735-43FA-ABA3-887BEE564628}" uniqueName="youtube" name="YT" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/utwory/utwor/youtube" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{99B4EC2A-A866-44AC-B852-0E6588653FC5}" uniqueName="4" name="Link do dysku" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D3A4E8F8-43C6-44AA-82EE-224D74326A0A}" uniqueName="5" name="Poziom" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{F99B30B8-346F-43E2-98A2-20AA45C6F763}" uniqueName="6" name="Opis" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{7B962474-3BFD-4D77-A67D-0E65A92583F0}" uniqueName="7" name="Tagi" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{99B4EC2A-A866-44AC-B852-0E6588653FC5}" uniqueName="4" name="Link do dysku" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{D3A4E8F8-43C6-44AA-82EE-224D74326A0A}" uniqueName="5" name="Poziom" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{F99B30B8-346F-43E2-98A2-20AA45C6F763}" uniqueName="6" name="Opis" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{7B962474-3BFD-4D77-A67D-0E65A92583F0}" uniqueName="7" name="Tagi" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="7" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>47</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="8" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>47</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>101</v>
@@ -2848,7 +2848,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>101</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>68</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>68</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>96</v>
@@ -3355,7 +3355,7 @@
         <v>44</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>311</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>96</v>
@@ -3374,7 +3374,7 @@
         <v>44</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>307</v>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEB1F70-8E0A-4C71-AD72-BA8CDFE04447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D99C62A-9512-42BB-9345-F50043675A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="370">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1140,6 +1140,9 @@
   </si>
   <si>
     <t>Ale Wkoło Jest Wesoło RIFF B</t>
+  </si>
+  <si>
+    <t>Nie wierz nigdy kobiecie RIFF B</t>
   </si>
 </sst>
 </file>
@@ -3365,7 +3368,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>96</v>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D99C62A-9512-42BB-9345-F50043675A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557406F9-47D2-466A-8D34-EE4038AE4F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="401">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1143,6 +1143,99 @@
   </si>
   <si>
     <t>Nie wierz nigdy kobiecie RIFF B</t>
+  </si>
+  <si>
+    <t>To bardzo szybki riff, łączący ze sobą wiele dodatkowych technik artykulacyjnych. Pamiętaj o przestrojeniu swojej gitary do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>Poćwiczysz tutaj technikę staccato, skracając wybrzmiewanie niemal wszystkich dźwięków.</t>
+  </si>
+  <si>
+    <t>Jest to wyjątkowa aranżacja tego riffu, która bardziej przypomina grę fingerstyle niż jego klasyczną formę. Przypomina trochę „Can’t Stop” zespołu Red Hot Chili Peppers.</t>
+  </si>
+  <si>
+    <t>Jest to riff zagrany za pomocą power chordów, które ze względu na przestrrojenie chwytasz płasko ułożonymi palcami. Działa to trochę jak mini poprzeczki barre.</t>
+  </si>
+  <si>
+    <t>To klasyczna przygrywka zagrana w całkiem prosty sposób na pojedynczych dźwiękach.</t>
+  </si>
+  <si>
+    <t>Ten riff nauczy Cię tłumienia poszczególnych dźwięków za pomocą wypłaszczonych palców, tak aby wybrzmiewały tylko te, które należy grać.</t>
+  </si>
+  <si>
+    <t>To bardzo trudna aranżacja fingerstyle, która łączy ze sobą wszystkie elementy tego riffu.</t>
+  </si>
+  <si>
+    <t>To dosyć prosty riff, który do granych akordów dodaje elementy legato.</t>
+  </si>
+  <si>
+    <t>Idealny riff dla początkujących, który przygotowałem w dwóch pozycjach na gryfie. Wybierz tę, która jest dla Ciebie lepsza.</t>
+  </si>
+  <si>
+    <t>Legendarny riff Nocnego Kochanka, który łączy ze sobą wiele technik artykulacyjnych. Swoją konstrukcją od zawsze przypominał mi „Master of Puppets”.</t>
+  </si>
+  <si>
+    <t>Ten riff łączy ze sobą wiele technik artykulacyjnych, takich jak legato, slide’y, vibrato oraz tłumienie nadgarstkiem.</t>
+  </si>
+  <si>
+    <t>To riff, dzięki któremu popracujesz nad string skippingiem oraz podciąganiem strun, które na początku może przysporzyć wiele problemów.</t>
+  </si>
+  <si>
+    <t>To riff, którego najtrudniejszym elementem jest szybkie przekładanie palca w celu zmiany dźwięków.</t>
+  </si>
+  <si>
+    <t>Charakterystyczna linia basowa, która zabrzmi dobrze, jeżeli opanujesz wybrzmiewanie pustych strun tak, aby na siebie nie zachodziły. Całość brzmi trochę w stylu country.</t>
+  </si>
+  <si>
+    <t>Legendarna linia basowa, która jest niemalże idealna dla początkujących gitarzystów.</t>
+  </si>
+  <si>
+    <t>To jeden z najtrudniejszych riffów, który świetnie nadaje się jako samodzielne ćwiczenie techniki. Skup się na kostkowaniu naprzemiennym oraz zmianie strun za pomocą pochylania płaszczyzny kostkowania.</t>
+  </si>
+  <si>
+    <t>To charakterystyczny bluesowy riff w rytmie shuffle. Można powiedzieć, że jest to Dżemowe podejście do klasyki bluesa.</t>
+  </si>
+  <si>
+    <t>To całkiem prosty riff, ale ma dosyć trudny moment łączący ze sobą techniki legato.</t>
+  </si>
+  <si>
+    <t>Ten riff łączy ze sobą długo wybrzmiewające dźwięki oraz technikę legato.</t>
+  </si>
+  <si>
+    <t>Ten riff mocno opiera się na brzmieniu wynikającym z selektywnego używania techniki tłumienia nadgarstkiem.</t>
+  </si>
+  <si>
+    <t>Świetny riff dla początkujących, dzięki któremu można wyćwiczyć rytmikę.</t>
+  </si>
+  <si>
+    <t>Bardzo prosty riff, który jest idealny dla początkujących.</t>
+  </si>
+  <si>
+    <t>Riff, który wykorzystuje dwudźwięki oraz ciekawe współbrzmienia.</t>
+  </si>
+  <si>
+    <t>To dosyć trudny riff, który przypomina trochę klasyczne kompozycje wykonywane na nylonowych strunach. Jest to must have dla wszystkich fanów zespołu Turbo.</t>
+  </si>
+  <si>
+    <t>To klasyczna przygrywka grana na niemalże każdym polskim weselu. Dodatkowo jest to świetny utwór dla początkujących.</t>
+  </si>
+  <si>
+    <t>Jest to najciężej brzmiący riff zagrany w stroju E Standard. Łączy ze sobą power chordy oraz slide’y.</t>
+  </si>
+  <si>
+    <t>Świetny riff dla początkujących. Wystarczy złapać akord i uderzyć kostką trzymane dźwięki.</t>
+  </si>
+  <si>
+    <t>Riff łączący ze sobą umiejętne opalcowanie dźwięków, technikę slide oraz staccato.</t>
+  </si>
+  <si>
+    <t>Klasyka polskiego bluesa, dzięki której nauczysz się pentatoniki, podciągania z odpuszczeniem oraz techniki staccato.</t>
+  </si>
+  <si>
+    <t>Stosunkowo prosty riff zbudowany w oparciu o kształt power chordów oraz sąsiadujące puste struny. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>Bardzo ciekawie brzmiący riff, zbudowany w oparciu o rytm shuffle. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
   </si>
 </sst>
 </file>
@@ -1239,17 +1332,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
@@ -1258,6 +1349,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1267,7 +1361,7 @@
   <dxfs count="8">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1280,15 +1374,10 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1496,8 +1585,8 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{99B4EC2A-A866-44AC-B852-0E6588653FC5}" uniqueName="4" name="Link do dysku" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{D3A4E8F8-43C6-44AA-82EE-224D74326A0A}" uniqueName="5" name="Poziom" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{F99B30B8-346F-43E2-98A2-20AA45C6F763}" uniqueName="6" name="Opis" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{7B962474-3BFD-4D77-A67D-0E65A92583F0}" uniqueName="7" name="Tagi" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{F99B30B8-346F-43E2-98A2-20AA45C6F763}" uniqueName="6" name="Opis" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{7B962474-3BFD-4D77-A67D-0E65A92583F0}" uniqueName="7" name="Tagi" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1826,9 +1915,9 @@
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="68.140625" customWidth="1"/>
+    <col min="6" max="6" width="61" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1856,2542 +1945,2604 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>190</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>191</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>340</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>341</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>192</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>194</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>196</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>197</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>200</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>201</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>202</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>203</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="6"/>
+      <c r="F21" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>205</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>206</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="6"/>
+      <c r="F23" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="C24" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>207</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>208</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="6"/>
+      <c r="F25" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="6"/>
+      <c r="F26" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>210</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="6"/>
+      <c r="F27" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="6"/>
+      <c r="F28" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>212</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="6" t="s">
+      <c r="F29" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>213</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="6" t="s">
+      <c r="F30" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>214</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="6" t="s">
+      <c r="F31" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="6"/>
+      <c r="F32" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>216</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="6"/>
+      <c r="F33" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="C34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>217</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="6"/>
+      <c r="F34" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="C35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>218</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="6" t="s">
+      <c r="F35" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="C36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>219</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="6"/>
+      <c r="F36" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="6"/>
+      <c r="F37" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="C38" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>221</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="6"/>
+      <c r="F38" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="C39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>222</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="6"/>
+      <c r="F39" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>223</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="6"/>
+      <c r="F40" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>224</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="6"/>
+      <c r="F41" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>225</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="6"/>
+      <c r="F42" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>226</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="6"/>
+      <c r="F43" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="C44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>227</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="6"/>
+      <c r="F44" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="6"/>
+      <c r="F45" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="C46" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>229</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="6"/>
+      <c r="F46" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>230</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="F47" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G47" s="5"/>
+    </row>
+    <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>231</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="6"/>
+      <c r="F48" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="G48" s="5"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>356</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="6" t="s">
+      <c r="F49" t="s">
+        <v>399</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>357</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="6" t="s">
+      <c r="F50" t="s">
+        <v>400</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="C51" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>232</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="6"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="C52" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>358</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="6"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="C53" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>359</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="6"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="C54" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>233</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="6"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="C55" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>234</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="6"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>235</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="6"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="3" t="s">
         <v>236</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="6"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="C58" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>237</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="6"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="3" t="s">
         <v>238</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="6"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="C60" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>239</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="6" t="s">
+      <c r="F60" s="5"/>
+      <c r="G60" s="5" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="3" t="s">
         <v>240</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="6"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>241</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="6"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="C63" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>242</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="6"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>243</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="6"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="3" t="s">
         <v>244</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="6"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="3" t="s">
         <v>245</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="6"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="C67" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>246</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="6"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="6"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="3" t="s">
         <v>248</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="6"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="4" t="s">
+      <c r="C70" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="6"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" s="4" t="s">
+      <c r="C71" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="6"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="C72" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>251</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="6"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="C73" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>252</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="6"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="C74" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="6"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="3" t="s">
         <v>254</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="6"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="C76" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>360</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="6"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" s="4" t="s">
+      <c r="C77" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>361</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="6"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="C78" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>255</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="6"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="C79" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>256</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="6"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D80" s="4" t="s">
+      <c r="C80" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="6"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" s="4" t="s">
+      <c r="C81" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>258</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="6"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="3" t="s">
         <v>259</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="6"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="C83" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>260</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="6"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="C84" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>261</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="6"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="C85" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>262</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="6"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="C86" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>263</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="6"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="3" t="s">
         <v>264</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="6"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="3" t="s">
         <v>265</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="6"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="C89" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>266</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="6"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="3" t="s">
         <v>267</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="6"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="6"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="3" t="s">
         <v>269</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="6"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="C93" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>270</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="6"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="C94" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>271</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="6"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="3" t="s">
         <v>272</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="6"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="C96" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>273</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="6"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D97" s="4" t="s">
+      <c r="C97" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>274</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="6"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="3" t="s">
         <v>275</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="6"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="6"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="C100" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>277</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="6"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" s="4" t="s">
+      <c r="C101" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>278</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="6"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C102" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="3" t="s">
         <v>279</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="6"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="C103" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>280</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="6"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="C104" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>281</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="6"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" s="5" t="s">
+      <c r="C105" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>282</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="6"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+      <c r="A106" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D106" s="4" t="s">
+      <c r="C106" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>283</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="6"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="3" t="s">
         <v>284</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F107" s="3"/>
-      <c r="G107" s="6"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="3" t="s">
         <v>285</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F108" s="3"/>
-      <c r="G108" s="6"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D109" s="4" t="s">
+      <c r="C109" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>286</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F109" s="3"/>
-      <c r="G109" s="6"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="3" t="s">
         <v>287</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F110" s="3"/>
-      <c r="G110" s="6"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D111" s="4" t="s">
+      <c r="C111" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>288</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="6"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="3" t="s">
         <v>289</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="6"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="9" t="s">
+      <c r="A113" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B113" s="9" t="s">
+      <c r="B113" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="C113" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>290</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="6"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C114" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="3" t="s">
         <v>291</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="6"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="9" t="s">
+      <c r="A115" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="C115" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>292</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="6"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="9" t="s">
+      <c r="A116" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D116" s="4" t="s">
+      <c r="C116" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>293</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="6"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="9" t="s">
+      <c r="A117" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D117" s="4" t="s">
+      <c r="C117" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>294</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="6"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="9" t="s">
+      <c r="A118" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D118" s="4" t="s">
+      <c r="C118" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="6"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="9" t="s">
+      <c r="A119" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D119" s="4" t="s">
+      <c r="C119" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>296</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="6"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="9" t="s">
+      <c r="A120" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D120" s="3" t="s">
         <v>297</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F120" s="3"/>
-      <c r="G120" s="6"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="9" t="s">
+      <c r="A121" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="C121" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>298</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="6"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="9" t="s">
+      <c r="A122" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D122" s="4" t="s">
+      <c r="C122" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>299</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F122" s="3"/>
-      <c r="G122" s="6"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="9" t="s">
+      <c r="A123" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B123" s="9" t="s">
+      <c r="B123" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C123" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D123" s="3" t="s">
         <v>300</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F123" s="3"/>
-      <c r="G123" s="6"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="9" t="s">
+      <c r="A124" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B124" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D124" s="3" t="s">
         <v>301</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F124" s="3"/>
-      <c r="G124" s="6"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="9" t="s">
+      <c r="A125" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D125" s="4" t="s">
+      <c r="C125" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>302</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F125" s="3"/>
-      <c r="G125" s="6"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="9" t="s">
+      <c r="A126" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C126" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="3" t="s">
         <v>303</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F126" s="3"/>
-      <c r="G126" s="6"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="9" t="s">
+      <c r="A127" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D127" s="3" t="s">
         <v>304</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F127" s="3"/>
-      <c r="G127" s="6" t="s">
+      <c r="F127" s="5"/>
+      <c r="G127" s="5" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="9" t="s">
+      <c r="A128" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B128" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D128" s="4" t="s">
+      <c r="C128" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>305</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F128" s="3"/>
-      <c r="G128" s="6"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B129" s="9" t="s">
+      <c r="B129" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129" s="4" t="s">
+      <c r="C129" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>306</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F129" s="3"/>
-      <c r="G129" s="6"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="4"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="3"/>
       <c r="E130" s="2"/>
-      <c r="F130" s="3"/>
-      <c r="G130" s="6"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="4"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="3"/>
       <c r="E131" s="2"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="6"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4403,11 +4554,23 @@
     <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{A1484470-F758-427A-8BC6-ADB24E480B76}"/>
     <hyperlink ref="D7" r:id="rId8" xr:uid="{422A23FB-E927-44A1-8543-D05FC652092F}"/>
+    <hyperlink ref="D20" r:id="rId9" xr:uid="{E76A0F70-467A-46BC-9D0C-8822598C03EE}"/>
+    <hyperlink ref="D22" r:id="rId10" xr:uid="{44C890B1-B23D-433D-BCA8-9B3DD0C8665E}"/>
+    <hyperlink ref="D23" r:id="rId11" xr:uid="{04317569-EF6F-401A-AFE3-B3A014E8C247}"/>
+    <hyperlink ref="D28" r:id="rId12" xr:uid="{A141318B-5D4F-4DAE-9F71-BBAF983A17E0}"/>
+    <hyperlink ref="D29" r:id="rId13" xr:uid="{0F2AB330-7A20-4901-B84F-17ADE245921C}"/>
+    <hyperlink ref="D30" r:id="rId14" xr:uid="{694CE14C-979E-430D-B27F-347F7DB60B56}"/>
+    <hyperlink ref="D33" r:id="rId15" xr:uid="{8E1289DE-644B-4568-86FD-A289EB412D4C}"/>
+    <hyperlink ref="D36" r:id="rId16" xr:uid="{FC1EBC83-64C5-40CC-A7AC-4AEC05C45018}"/>
+    <hyperlink ref="D39" r:id="rId17" xr:uid="{0DD4BD01-0A8F-4B8A-A38F-60ACEC2B3CB3}"/>
+    <hyperlink ref="D43" r:id="rId18" xr:uid="{88871998-F5FA-4385-9619-661618D0882D}"/>
+    <hyperlink ref="D49" r:id="rId19" xr:uid="{AA084126-1AB3-452F-9A3C-555758045A85}"/>
+    <hyperlink ref="D50" r:id="rId20" xr:uid="{4D2316C6-1002-41AC-BA0F-4B06BF20AE03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667A7DA2-8385-499F-80A8-556A0BA208F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A59B80-A627-4A1B-BAA1-ACD010799BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="-105" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="403">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1236,6 +1236,12 @@
   </si>
   <si>
     <t>Bardzo ciekawie brzmiący riff, zbudowany w oparciu o rytm shuffle. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1H_78brL5cpJyEybM9al8QrLgga0DlxRm&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Dwa słowa dwa światy</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1352,6 +1358,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1915,7 +1925,7 @@
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="61" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
@@ -2570,162 +2580,160 @@
         <v>337</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>214</v>
+        <v>42</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="C33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F32" s="12" t="s">
+      <c r="E33" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F33" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="C34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="C35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>59</v>
@@ -2733,83 +2741,83 @@
       <c r="C37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>220</v>
+      <c r="D37" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>221</v>
+      <c r="D38" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>308</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>222</v>
+      <c r="D39" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>47</v>
@@ -2818,204 +2826,202 @@
         <v>44</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>310</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F44" s="12" t="s">
         <v>393</v>
-      </c>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>394</v>
       </c>
       <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G48" s="5"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>362</v>
+        <v>99</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>356</v>
+      <c r="D49" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F49" t="s">
-        <v>399</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>337</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="G49" s="5"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>101</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F50" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>337</v>
@@ -3023,45 +3029,49 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>102</v>
+        <v>363</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>232</v>
+      <c r="D51" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>364</v>
+        <v>102</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>358</v>
+        <v>232</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>68</v>
@@ -3070,7 +3080,7 @@
         <v>44</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>308</v>
@@ -3080,16 +3090,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>308</v>
@@ -3099,73 +3109,73 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>235</v>
+        <v>44</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>236</v>
+      <c r="D57" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>309</v>
@@ -3175,16 +3185,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>309</v>
@@ -3194,47 +3204,47 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F60" s="5"/>
-      <c r="G60" s="5" t="s">
-        <v>338</v>
-      </c>
+      <c r="G60" s="5"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="G61" s="5" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>43</v>
@@ -3243,64 +3253,64 @@
         <v>42</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>243</v>
+        <v>44</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>244</v>
+      <c r="D65" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>307</v>
@@ -3310,16 +3320,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>307</v>
@@ -3329,92 +3339,92 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>246</v>
+        <v>42</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>247</v>
+        <v>44</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>308</v>
@@ -3424,16 +3434,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>308</v>
@@ -3443,54 +3453,54 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>308</v>
@@ -3500,26 +3510,26 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>366</v>
+        <v>127</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>96</v>
@@ -3528,83 +3538,83 @@
         <v>44</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>128</v>
+        <v>369</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>255</v>
+        <v>361</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>307</v>
@@ -3614,54 +3624,54 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>308</v>
@@ -3671,16 +3681,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>308</v>
@@ -3690,16 +3700,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>308</v>
@@ -3709,92 +3719,92 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>307</v>
@@ -3804,54 +3814,54 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>323</v>
+        <v>145</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>44</v>
+        <v>147</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>308</v>
@@ -3861,16 +3871,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>308</v>
@@ -3880,35 +3890,35 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>307</v>
@@ -3918,16 +3928,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>307</v>
@@ -3937,35 +3947,35 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>324</v>
+        <v>155</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>310</v>
@@ -3975,64 +3985,64 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>43</v>
@@ -4041,26 +4051,26 @@
         <v>44</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>282</v>
+      <c r="D105" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>307</v>
@@ -4070,130 +4080,130 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>283</v>
+      <c r="D106" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>325</v>
+        <v>163</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>307</v>
@@ -4203,73 +4213,73 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>167</v>
+        <v>5</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>307</v>
@@ -4279,54 +4289,54 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>307</v>
@@ -4336,16 +4346,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>322</v>
+        <v>173</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>307</v>
@@ -4355,73 +4365,73 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>44</v>
+      <c r="C121" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>308</v>
@@ -4431,85 +4441,85 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F127" s="5"/>
-      <c r="G127" s="5" t="s">
-        <v>315</v>
-      </c>
+      <c r="G127" s="5"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F128" s="5"/>
-      <c r="G128" s="5"/>
+      <c r="G128" s="5" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>43</v>
@@ -4518,20 +4528,30 @@
         <v>44</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="2"/>
+      <c r="A130" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
     </row>
@@ -4546,10 +4566,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C120" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
-    <hyperlink ref="C92" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
-    <hyperlink ref="C99" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
-    <hyperlink ref="C110" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
+    <hyperlink ref="C121" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
+    <hyperlink ref="C93" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
+    <hyperlink ref="C100" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
+    <hyperlink ref="C111" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
     <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{A1484470-F758-427A-8BC6-ADB24E480B76}"/>
@@ -4559,18 +4579,19 @@
     <hyperlink ref="D23" r:id="rId11" xr:uid="{04317569-EF6F-401A-AFE3-B3A014E8C247}"/>
     <hyperlink ref="D28" r:id="rId12" xr:uid="{A141318B-5D4F-4DAE-9F71-BBAF983A17E0}"/>
     <hyperlink ref="D29" r:id="rId13" xr:uid="{0F2AB330-7A20-4901-B84F-17ADE245921C}"/>
-    <hyperlink ref="D30" r:id="rId14" xr:uid="{694CE14C-979E-430D-B27F-347F7DB60B56}"/>
-    <hyperlink ref="D33" r:id="rId15" xr:uid="{8E1289DE-644B-4568-86FD-A289EB412D4C}"/>
-    <hyperlink ref="D36" r:id="rId16" xr:uid="{FC1EBC83-64C5-40CC-A7AC-4AEC05C45018}"/>
-    <hyperlink ref="D39" r:id="rId17" xr:uid="{0DD4BD01-0A8F-4B8A-A38F-60ACEC2B3CB3}"/>
-    <hyperlink ref="D43" r:id="rId18" xr:uid="{88871998-F5FA-4385-9619-661618D0882D}"/>
-    <hyperlink ref="D49" r:id="rId19" xr:uid="{AA084126-1AB3-452F-9A3C-555758045A85}"/>
-    <hyperlink ref="D50" r:id="rId20" xr:uid="{4D2316C6-1002-41AC-BA0F-4B06BF20AE03}"/>
+    <hyperlink ref="D31" r:id="rId14" xr:uid="{694CE14C-979E-430D-B27F-347F7DB60B56}"/>
+    <hyperlink ref="D34" r:id="rId15" xr:uid="{8E1289DE-644B-4568-86FD-A289EB412D4C}"/>
+    <hyperlink ref="D37" r:id="rId16" xr:uid="{FC1EBC83-64C5-40CC-A7AC-4AEC05C45018}"/>
+    <hyperlink ref="D40" r:id="rId17" xr:uid="{0DD4BD01-0A8F-4B8A-A38F-60ACEC2B3CB3}"/>
+    <hyperlink ref="D44" r:id="rId18" xr:uid="{88871998-F5FA-4385-9619-661618D0882D}"/>
+    <hyperlink ref="D50" r:id="rId19" xr:uid="{AA084126-1AB3-452F-9A3C-555758045A85}"/>
+    <hyperlink ref="D51" r:id="rId20" xr:uid="{4D2316C6-1002-41AC-BA0F-4B06BF20AE03}"/>
+    <hyperlink ref="D30" r:id="rId21" xr:uid="{C55DAD92-5FDC-4B1A-BC1B-7056726B6F79}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A59B80-A627-4A1B-BAA1-ACD010799BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97854CFC-755A-48E9-9647-0064EBA93AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="404">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1242,6 +1242,9 @@
   </si>
   <si>
     <t>Dwa słowa dwa światy</t>
+  </si>
+  <si>
+    <t>DATA</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1341,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1362,6 +1365,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1578,12 +1582,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:G131" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
-  <autoFilter ref="A1:G131" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:H131" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
+  <autoFilter ref="A1:H131" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G131">
     <sortCondition ref="A1:A131"/>
   </sortState>
-  <tableColumns count="7">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6FF1AA77-FAFD-461A-9D1E-E1F2F29A966E}" uniqueName="tytul" name="UTWÓR" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/utwory/utwor/tytul" xmlDataType="string"/>
     </tableColumn>
@@ -1597,6 +1601,7 @@
     <tableColumn id="5" xr3:uid="{D3A4E8F8-43C6-44AA-82EE-224D74326A0A}" uniqueName="5" name="Poziom" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{F99B30B8-346F-43E2-98A2-20AA45C6F763}" uniqueName="6" name="Opis" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{7B962474-3BFD-4D77-A67D-0E65A92583F0}" uniqueName="7" name="Tagi" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{25B00C7B-E57A-4A7B-A525-9040FA6AB0BF}" uniqueName="8" name="DATA"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1919,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
@@ -1929,9 +1934,10 @@
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="61" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>185</v>
       </c>
@@ -1953,8 +1959,11 @@
       <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
@@ -1977,7 +1986,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>30</v>
       </c>
@@ -2000,7 +2009,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -2023,7 +2032,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
@@ -2043,8 +2052,11 @@
         <v>321</v>
       </c>
       <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="H5" s="15">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -2067,7 +2079,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>367</v>
       </c>
@@ -2090,7 +2102,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>368</v>
       </c>
@@ -2113,7 +2125,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
@@ -2136,7 +2148,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>50</v>
       </c>
@@ -2159,7 +2171,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
@@ -2182,7 +2194,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>0</v>
       </c>
@@ -2205,7 +2217,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>54</v>
       </c>
@@ -2228,7 +2240,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>56</v>
       </c>
@@ -2251,7 +2263,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>57</v>
       </c>
@@ -2274,7 +2286,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>8</v>
       </c>
@@ -2297,7 +2309,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>61</v>
       </c>
@@ -2320,7 +2332,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>63</v>
       </c>
@@ -2343,7 +2355,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
@@ -2364,7 +2376,7 @@
       </c>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>66</v>
       </c>
@@ -2387,7 +2399,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
@@ -2408,7 +2420,7 @@
       </c>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>69</v>
       </c>
@@ -2429,7 +2441,7 @@
       </c>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>71</v>
       </c>
@@ -2450,7 +2462,7 @@
       </c>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>72</v>
       </c>
@@ -2473,7 +2485,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>74</v>
       </c>
@@ -2494,7 +2506,7 @@
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>75</v>
       </c>
@@ -2515,7 +2527,7 @@
       </c>
       <c r="G26" s="5"/>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>77</v>
       </c>
@@ -2536,7 +2548,7 @@
       </c>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>78</v>
       </c>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>80</v>
       </c>
@@ -2580,7 +2592,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>402</v>
       </c>
@@ -2598,8 +2610,11 @@
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="H30" s="15">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>23</v>
       </c>
@@ -2622,7 +2637,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>24</v>
       </c>
@@ -3907,7 +3922,7 @@
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>152</v>
       </c>
@@ -3926,7 +3941,7 @@
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>153</v>
       </c>
@@ -3945,7 +3960,7 @@
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>154</v>
       </c>
@@ -3964,7 +3979,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>156</v>
       </c>
@@ -3983,7 +3998,7 @@
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>13</v>
       </c>
@@ -4002,7 +4017,7 @@
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>22</v>
       </c>
@@ -4021,7 +4036,7 @@
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>19</v>
       </c>
@@ -4040,7 +4055,7 @@
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>14</v>
       </c>
@@ -4059,7 +4074,7 @@
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>159</v>
       </c>
@@ -4078,7 +4093,7 @@
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>3</v>
       </c>
@@ -4097,7 +4112,7 @@
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>15</v>
       </c>
@@ -4115,8 +4130,11 @@
       </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" s="15">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>160</v>
       </c>
@@ -4135,7 +4153,7 @@
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>161</v>
       </c>
@@ -4154,7 +4172,7 @@
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>162</v>
       </c>
@@ -4173,7 +4191,7 @@
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>33</v>
       </c>
@@ -4192,7 +4210,7 @@
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>16</v>
       </c>
@@ -4211,7 +4229,7 @@
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>164</v>
       </c>
@@ -4230,7 +4248,7 @@
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>166</v>
       </c>
@@ -4249,7 +4267,7 @@
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>5</v>
       </c>
@@ -4268,7 +4286,7 @@
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>167</v>
       </c>
@@ -4287,7 +4305,7 @@
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>6</v>
       </c>
@@ -4306,7 +4324,7 @@
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>169</v>
       </c>
@@ -4325,7 +4343,7 @@
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>171</v>
       </c>
@@ -4344,7 +4362,7 @@
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>172</v>
       </c>
@@ -4363,7 +4381,7 @@
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>174</v>
       </c>
@@ -4382,7 +4400,7 @@
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>176</v>
       </c>
@@ -4401,7 +4419,7 @@
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>177</v>
       </c>
@@ -4419,8 +4437,11 @@
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" s="15">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>178</v>
       </c>
@@ -4439,7 +4460,7 @@
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>179</v>
       </c>
@@ -4458,7 +4479,7 @@
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>181</v>
       </c>
@@ -4477,7 +4498,7 @@
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>183</v>
       </c>
@@ -4496,7 +4517,7 @@
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>184</v>
       </c>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97854CFC-755A-48E9-9647-0064EBA93AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06076B68-7F3F-48F6-A11D-2DE30376A424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="405">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1245,6 +1245,9 @@
   </si>
   <si>
     <t>DATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skala, Kostkowanie w dół, </t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2054,9 @@
       <c r="F5" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>404</v>
+      </c>
       <c r="H5" s="15">
         <v>46205</v>
       </c>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06076B68-7F3F-48F6-A11D-2DE30376A424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5F73A3-EC8C-4B55-9DA7-D1E0D132057C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5F73A3-EC8C-4B55-9DA7-D1E0D132057C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910F7824-6E14-47CA-8F4A-6A5DD5C58923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="467">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -161,15 +161,9 @@
     <t>Coma</t>
   </si>
   <si>
-    <t>Tak</t>
-  </si>
-  <si>
     <t>Lady Pank</t>
   </si>
   <si>
-    <t>Nie</t>
-  </si>
-  <si>
     <t>A to ohyda</t>
   </si>
   <si>
@@ -1248,6 +1242,198 @@
   </si>
   <si>
     <t xml:space="preserve">Skala, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ciekawy Riff który wykorzystuje melodię graną na strunie G3 oraz dwie puste struny poniżej. Genialne brzmienie. </t>
+  </si>
+  <si>
+    <t>Puste struny, Melodia</t>
+  </si>
+  <si>
+    <t>Ten Riff wykorzystuje wspóbrzmienie kilku dźwięków oraz efekt Tremolo.</t>
+  </si>
+  <si>
+    <t>Legendarne intro z melodią graną na tle akordów oraz wstawkami w stylu Hendrixa.</t>
+  </si>
+  <si>
+    <t>Nauczysz się ogrywać akordy z dodatkiem techniki legato. Dodaj efekt Tremolo.</t>
+  </si>
+  <si>
+    <t>Klimatyczny Bluesowy Riff z dodatkiem "Micro Bendów" o pół tonu oraz techniką "Palm Mute"</t>
+  </si>
+  <si>
+    <t>Palm mute, Podciąganie strun</t>
+  </si>
+  <si>
+    <t>Odpal efekt Wah Wah i zagraj ten Riff na pojedyńczych dźwiękach i dwudźwiękach w stylu Hendrixa.</t>
+  </si>
+  <si>
+    <t>Wah Wah, Dwudźwięki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riff oparty w całości o powerchordy grane wzdłóż gryfu. </t>
+  </si>
+  <si>
+    <t>Power chordy, Kostkowanie w dół.</t>
+  </si>
+  <si>
+    <t>To bardzo melodyjny riff którego granie sprawia wiele radości</t>
+  </si>
+  <si>
+    <t>Melodia,</t>
+  </si>
+  <si>
+    <t>Ten riff polega na graniu dwudźwięków przesuwanych wzdłuż gryfu.</t>
+  </si>
+  <si>
+    <t>dwudźwięki,</t>
+  </si>
+  <si>
+    <t>Bardzo egzotycznie brzmiące Riff który wykorzystuje specyficzne podciąganie strun.</t>
+  </si>
+  <si>
+    <t>Podciąganie strun</t>
+  </si>
+  <si>
+    <t>Riff mieszający ze sobą wiele technik gitarowych</t>
+  </si>
+  <si>
+    <t>https://youtu.be/YLzc_Te82L0?si=URyba-DOiMn9R3xq</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yh-QyzlND68?si=qBDGUp4hYpSfq39J</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uQmCetlsl88?si=ut4ZOdvWXcX3VZsS</t>
+  </si>
+  <si>
+    <t>https://youtu.be/l7oTgVPveS8?si=EhnYVNmW_Ng661vP</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JYZADpVWCas?si=d3Us04b9yWTJuJQK</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2zBpKWogrY0?si=KoQtNgo7lJ6hwUUY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TvMh3PlmnQo?si=aCLudIi-qG_n5N5S</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sBjXceEdbX4?si=WtxzdpFBnOh2a5HV</t>
+  </si>
+  <si>
+    <t>https://youtu.be/h4EbBy5vakA?si=bdADJ90AJjLI63KO</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SFdQKGArMmA?si=mGRFveu6htSeFKqL</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NvLb1QVQW3c?si=zA3lJjKvBEMmCe_O</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ls1Adbhu3eA?si=cyEZXTKXsFIc_Iml</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-LEurFVbjiI?si=CiThYP0u4O0VljzY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_x7aEWkqJ5o?si=DKtCoN7OvcNKeVb7</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JwvabslN010?si=TB6pQhVI7xfg9maw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Xp1-j1zPdIA?si=X1Ce9NWjSdoRo-3y</t>
+  </si>
+  <si>
+    <t>https://youtu.be/D2FjfdQm-ng?si=6dUfwsjBL2_TNFTU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y7p5UJfaBcQ?si=hdcyOA1emQVcP_XG</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fDvtNYuaLYY?si=-8fzqmoUD8nRFAyY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/n4zuKc1PDQM?si=sCPHNUhVPRUgCEL0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6i_bwVz0v3Q?si=WhfA4-IXO5zs4_h1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CtS-eIYHWN0?si=BYd0Wpu5PZMUh_41</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aIiHZl_o5g8?si=8F6XZehsgDzrjNel</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aiYGm7oTAhw?si=S-WwYHtSlthUf2fX</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ueb2VIuF8ao?si=yVCwcWlpH40-Ndh7</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kmSStS8rVl4?si=n9XmzA3iThj6xd7g</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uyX-97bt3AI?si=_UoYaxga_NgmiK_0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SFsVDehcS-0?si=cHx2Dvh573mMuHEN</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DSFBiQGZUG8?si=HBGg-ROligepYGEi</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3E_Xliw2L2M?si=OUpARa-ZTqJEtDNL</t>
+  </si>
+  <si>
+    <t>https://youtu.be/lJf-Br4EWOA?si=jw2MtAu2w4dWnQrE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/laj4lD58fe0?si=dmlh-ZtFHZDG7qBM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VL5_vO1aIr0?si=9Bl3xbjbxOOWsry-</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_f64mKvYTV8?si=9IRAYDVknVKiXWmw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pGzBvQmwVLU?si=tTB9gbYoTMEzg7wU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Kk84kkUJ0Dk?si=RNh28UwuQSZC-Kjk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pqLmSFjnUcs?si=ixsRGQA5pMe8gIJB</t>
+  </si>
+  <si>
+    <t>https://youtu.be/b2FJDXdhbVU?si=VwHxPrcE0_MDN5_4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QIzkPULxs2c?si=mloB9U8jLBuT7brx</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ADGnivroQ3Y?si=kO75g03N51jYyYZS</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7cDc6QUGNqo?si=M0odyZWmsWYAngbI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0_fBUBOxpTc?si=pI2ArUU7bNItWhqO</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R5fgRN3OJiY?si=674eAUBhBskH6TAT</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uqUPx1-JLp0?si=B-ZHpMWLQ11WXdCI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ov9-quLAidc?si=yNsnSeIQmEm_4l-4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SjtwCo2QJFE</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1530,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1369,6 +1555,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1942,10 +2129,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
@@ -1963,7 +2150,7 @@
         <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1973,20 +2160,20 @@
       <c r="B2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>42</v>
+      <c r="C2" s="16" t="s">
+        <v>439</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1996,20 +2183,20 @@
       <c r="B3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>42</v>
+      <c r="C3" s="16" t="s">
+        <v>460</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2017,45 +2204,41 @@
         <v>9</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C4" s="8"/>
       <c r="D4" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H5" s="15">
         <v>46205</v>
@@ -2066,114 +2249,112 @@
         <v>20</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>450</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>342</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C9" s="8"/>
       <c r="D9" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>446</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2181,22 +2362,22 @@
         <v>32</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>462</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2204,91 +2385,85 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C12" s="8"/>
       <c r="D12" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C13" s="8"/>
       <c r="D13" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C14" s="8"/>
       <c r="D14" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>56</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>429</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2296,112 +2471,108 @@
         <v>8</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C17" s="8"/>
       <c r="D17" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>447</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>42</v>
+        <v>65</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>457</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2409,209 +2580,197 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C21" s="8"/>
       <c r="D21" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C22" s="8"/>
       <c r="D22" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>42</v>
+      <c r="C23" s="16" t="s">
+        <v>451</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C24" s="8"/>
       <c r="D24" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>42</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>453</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>445</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C27" s="8"/>
       <c r="D27" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>42</v>
+        <v>77</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>433</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C29" s="8"/>
       <c r="D29" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>44</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C30" s="11"/>
       <c r="D30" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="5"/>
@@ -2624,22 +2783,22 @@
         <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>42</v>
+        <v>65</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>427</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2647,84 +2806,76 @@
         <v>24</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C32" s="8"/>
       <c r="D32" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C33" s="8"/>
       <c r="D33" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C34" s="8"/>
       <c r="D34" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C35" s="8"/>
       <c r="D35" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G35" s="5"/>
     </row>
@@ -2733,105 +2884,95 @@
         <v>1</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C36" s="8"/>
       <c r="D36" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C37" s="8"/>
       <c r="D37" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C38" s="8"/>
       <c r="D38" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C39" s="8"/>
       <c r="D39" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C40" s="8"/>
       <c r="D40" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G40" s="5"/>
     </row>
@@ -2840,40 +2981,36 @@
         <v>25</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C41" s="8"/>
       <c r="D41" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C42" s="8"/>
       <c r="D42" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G42" s="5"/>
     </row>
@@ -2882,82 +3019,80 @@
         <v>4</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>42</v>
+        <v>57</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>42</v>
+        <v>77</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>464</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C45" s="8"/>
       <c r="D45" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>42</v>
+        <v>94</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>465</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G46" s="5"/>
     </row>
@@ -2966,182 +3101,170 @@
         <v>2</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C47" s="8"/>
       <c r="D47" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>42</v>
+        <v>96</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>428</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G48" s="5"/>
     </row>
     <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>423</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G49" s="5"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>42</v>
+        <v>99</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>455</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F50" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="C51" s="8"/>
       <c r="D51" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C52" s="8"/>
       <c r="D52" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C53" s="8"/>
       <c r="D53" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C54" s="8"/>
       <c r="D54" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C55" s="8"/>
       <c r="D55" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3151,16 +3274,14 @@
         <v>31</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C56" s="8"/>
       <c r="D56" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3170,35 +3291,35 @@
         <v>10</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="C57" s="16" t="s">
+        <v>454</v>
+      </c>
       <c r="D57" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>42</v>
+        <v>57</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>441</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3208,75 +3329,71 @@
         <v>26</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C59" s="8"/>
       <c r="D59" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>42</v>
+      <c r="C60" s="16" t="s">
+        <v>448</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C61" s="8"/>
       <c r="D61" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="C62" s="16" t="s">
+        <v>461</v>
+      </c>
       <c r="D62" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3286,16 +3403,16 @@
         <v>11</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="C63" s="16" t="s">
+        <v>466</v>
+      </c>
       <c r="D63" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3305,16 +3422,14 @@
         <v>7</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C64" s="8"/>
       <c r="D64" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3324,149 +3439,143 @@
         <v>12</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="C65" s="16" t="s">
+        <v>458</v>
+      </c>
       <c r="D65" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>42</v>
+        <v>112</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>421</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>42</v>
+        <v>94</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C68" s="8"/>
       <c r="D68" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>432</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>42</v>
+        <v>117</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>442</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C71" s="8"/>
       <c r="D71" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C72" s="8"/>
       <c r="D72" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3476,130 +3585,118 @@
         <v>27</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C73" s="8"/>
       <c r="D73" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C74" s="8"/>
       <c r="D74" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C75" s="8"/>
       <c r="D75" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>42</v>
+        <v>66</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>452</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C77" s="8"/>
       <c r="D77" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C78" s="8"/>
       <c r="D78" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="C79" s="8"/>
       <c r="D79" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3609,54 +3706,48 @@
         <v>28</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C80" s="8"/>
       <c r="D80" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C81" s="8"/>
       <c r="D81" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C82" s="8"/>
       <c r="D82" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -3666,339 +3757,321 @@
         <v>29</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>434</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C84" s="8"/>
       <c r="D84" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C85" s="8"/>
       <c r="D85" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C86" s="8"/>
       <c r="D86" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C87" s="8"/>
       <c r="D87" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>42</v>
+        <v>136</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>449</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>425</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C90" s="8"/>
       <c r="D90" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>42</v>
+        <v>103</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>440</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>42</v>
+        <v>143</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>424</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C94" s="8"/>
       <c r="D94" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C95" s="8"/>
       <c r="D95" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>42</v>
+        <v>149</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>430</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C97" s="8"/>
       <c r="D97" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C98" s="8"/>
       <c r="D98" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>42</v>
+        <v>153</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>435</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
@@ -4008,16 +4081,14 @@
         <v>13</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C101" s="8"/>
       <c r="D101" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
@@ -4027,16 +4098,14 @@
         <v>22</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C102" s="8"/>
       <c r="D102" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -4046,16 +4115,16 @@
         <v>19</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>42</v>
+        <v>156</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>422</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -4065,35 +4134,31 @@
         <v>14</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C104" s="8"/>
       <c r="D104" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C105" s="8"/>
       <c r="D105" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
@@ -4103,16 +4168,14 @@
         <v>3</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C106" s="8"/>
       <c r="D106" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
@@ -4122,16 +4185,14 @@
         <v>15</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C107" s="8"/>
       <c r="D107" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
@@ -4141,57 +4202,55 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>42</v>
+        <v>136</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>438</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>431</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C110" s="8"/>
       <c r="D110" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
@@ -4201,16 +4260,16 @@
         <v>33</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
@@ -4220,54 +4279,50 @@
         <v>16</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C112" s="8"/>
       <c r="D112" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>42</v>
+        <v>163</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C114" s="8"/>
       <c r="D114" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
@@ -4277,35 +4332,33 @@
         <v>5</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>42</v>
+        <v>57</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>444</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C116" s="8"/>
       <c r="D116" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
@@ -4315,271 +4368,289 @@
         <v>6</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C117" s="8"/>
       <c r="D117" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C118" s="8"/>
       <c r="D118" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" s="8"/>
+      <c r="D119" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="G119" s="5"/>
+    </row>
+    <row r="120" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B119" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="C120" s="8"/>
       <c r="D120" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F120" s="5"/>
+        <v>305</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="G120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B121" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="B122" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C122" s="8"/>
       <c r="D122" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
+        <v>306</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C123" s="8"/>
       <c r="D123" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
+        <v>305</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>415</v>
+      </c>
       <c r="H123" s="15">
         <v>46206</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B125" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B124" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C124" s="8" t="s">
+      <c r="C125" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" s="8"/>
+      <c r="D126" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G127" s="5"/>
+    </row>
+    <row r="128" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D126" s="3" t="s">
+      <c r="C128" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="E128" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F128" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>406</v>
+      </c>
       <c r="G128" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C129" s="8"/>
       <c r="D129" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F129" s="5"/>
+        <v>306</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>405</v>
+      </c>
       <c r="G129" s="5"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C130" s="8"/>
       <c r="D130" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
+        <v>305</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
@@ -4613,11 +4684,57 @@
     <hyperlink ref="D50" r:id="rId19" xr:uid="{AA084126-1AB3-452F-9A3C-555758045A85}"/>
     <hyperlink ref="D51" r:id="rId20" xr:uid="{4D2316C6-1002-41AC-BA0F-4B06BF20AE03}"/>
     <hyperlink ref="D30" r:id="rId21" xr:uid="{C55DAD92-5FDC-4B1A-BC1B-7056726B6F79}"/>
+    <hyperlink ref="C66" r:id="rId22" xr:uid="{0D0886A2-F3C3-480C-ACB5-7E9F5604BEE1}"/>
+    <hyperlink ref="C103" r:id="rId23" xr:uid="{1B2DCF39-CE87-4563-8C23-4B4C16C724D0}"/>
+    <hyperlink ref="C49" r:id="rId24" xr:uid="{DF5EA4AA-71D1-4C9E-89DF-C5D89BC4E6E2}"/>
+    <hyperlink ref="C92" r:id="rId25" xr:uid="{7D3098E7-FC63-41D2-96A8-059BE5472EE9}"/>
+    <hyperlink ref="C89" r:id="rId26" xr:uid="{4A06348E-5CCD-42E1-AEE9-DDEB145C1218}"/>
+    <hyperlink ref="C127" r:id="rId27" xr:uid="{81755034-E021-4201-A21B-AA31E5C0583C}"/>
+    <hyperlink ref="C31" r:id="rId28" xr:uid="{BFD84D1C-A8F0-47FB-A7D2-69E8F11F7E3A}"/>
+    <hyperlink ref="C48" r:id="rId29" xr:uid="{884134B3-78F7-4B64-975F-F8A35B1797C6}"/>
+    <hyperlink ref="C15" r:id="rId30" xr:uid="{0F59C3F4-D333-4384-9892-75DAAA2949DF}"/>
+    <hyperlink ref="C96" r:id="rId31" xr:uid="{65BEB210-CD11-4EDB-87B0-586A9AEAF1A1}"/>
+    <hyperlink ref="C109" r:id="rId32" xr:uid="{C16B2635-5E40-43E0-B53C-231E6B5BA338}"/>
+    <hyperlink ref="C69" r:id="rId33" xr:uid="{8289369F-FDE5-41F5-82D3-17980A1A515D}"/>
+    <hyperlink ref="C28" r:id="rId34" xr:uid="{BAADA460-3F16-4211-84B0-B950477C827C}"/>
+    <hyperlink ref="C83" r:id="rId35" xr:uid="{10B2AA87-445F-4E32-86E5-2FB98D5F55C0}"/>
+    <hyperlink ref="C99" r:id="rId36" xr:uid="{7FC87147-D271-4512-99EB-F85A26817E52}"/>
+    <hyperlink ref="C43" r:id="rId37" xr:uid="{1AB02971-7B46-4D5E-A6F0-02E39FDE3773}"/>
+    <hyperlink ref="C113" r:id="rId38" xr:uid="{EBEDDBA0-4FE4-44D6-BA62-97800EE20F5B}"/>
+    <hyperlink ref="C108" r:id="rId39" xr:uid="{A7536EA9-5089-48A4-9B13-3A1A92148A3E}"/>
+    <hyperlink ref="C2" r:id="rId40" xr:uid="{A5D68F30-26BA-4BEC-A688-D6DB7044B172}"/>
+    <hyperlink ref="C91" r:id="rId41" xr:uid="{4A19AE74-91EF-4534-B3DF-DF871E873117}"/>
+    <hyperlink ref="C58" r:id="rId42" xr:uid="{35B503EE-4E80-4459-B837-807BDD329C63}"/>
+    <hyperlink ref="C70" r:id="rId43" xr:uid="{FBC908B1-05DF-4C49-9A2F-5F17FF5D8E9E}"/>
+    <hyperlink ref="C124" r:id="rId44" xr:uid="{235DA5D8-F14A-4D11-A2E7-D94645958288}"/>
+    <hyperlink ref="C115" r:id="rId45" xr:uid="{15F28079-C550-4515-BD54-221F79B5DEC8}"/>
+    <hyperlink ref="C26" r:id="rId46" xr:uid="{D5FC560A-2D8C-4AF5-85B1-2D0CB6A5BA4E}"/>
+    <hyperlink ref="C10" r:id="rId47" xr:uid="{EC42F027-8AEF-4A1D-A766-3005FB7F4C38}"/>
+    <hyperlink ref="C18" r:id="rId48" xr:uid="{16F2FF4E-6553-4E49-AC6D-DD98577CE855}"/>
+    <hyperlink ref="C60" r:id="rId49" xr:uid="{EEB47972-38D6-477B-AE6F-A6B6014F91B2}"/>
+    <hyperlink ref="C88" r:id="rId50" xr:uid="{6E05623E-8723-479B-8FA4-ECC0C19ADD3F}"/>
+    <hyperlink ref="C6" r:id="rId51" xr:uid="{C82974F8-4A5E-4C06-878A-E20FD0E16912}"/>
+    <hyperlink ref="C23" r:id="rId52" xr:uid="{7C727B88-9CEA-4BED-8AD0-BE9CABE06637}"/>
+    <hyperlink ref="C76" r:id="rId53" xr:uid="{203DBE26-1375-4C8E-9C21-39E5891065AD}"/>
+    <hyperlink ref="C25" r:id="rId54" xr:uid="{0C11A83D-52E2-47CA-A7E0-FAEAC26EA00D}"/>
+    <hyperlink ref="C57" r:id="rId55" xr:uid="{EC7DD2F0-EEE6-4CE4-9B34-50155D12B60C}"/>
+    <hyperlink ref="C50" r:id="rId56" xr:uid="{AAA4DA5D-97DD-45DA-B0EC-84BDB682F262}"/>
+    <hyperlink ref="C67" r:id="rId57" xr:uid="{E23A3F1D-5EEC-420F-ACA7-5A86E8BF04DA}"/>
+    <hyperlink ref="C20" r:id="rId58" xr:uid="{D105BCCF-FC90-4E54-BC81-C996C187AC4A}"/>
+    <hyperlink ref="C65" r:id="rId59" xr:uid="{51FBB38A-71B9-4116-BBD1-49B100307458}"/>
+    <hyperlink ref="C125" r:id="rId60" xr:uid="{2DB17360-68D0-449D-820E-8C8690BF9FAC}"/>
+    <hyperlink ref="C3" r:id="rId61" xr:uid="{57F20C02-54C2-4CF8-B975-DBD3502042DD}"/>
+    <hyperlink ref="C62" r:id="rId62" xr:uid="{1FD68017-274E-4229-A827-8FCF6E75BE2B}"/>
+    <hyperlink ref="C11" r:id="rId63" xr:uid="{45505C35-932B-4754-AC3B-F502BBCE841A}"/>
+    <hyperlink ref="C128" r:id="rId64" xr:uid="{28B53600-84D9-432C-A477-C6F38FCFD596}"/>
+    <hyperlink ref="C44" r:id="rId65" xr:uid="{B39D759F-69F5-4DB1-829A-227F38BC01C9}"/>
+    <hyperlink ref="C46" r:id="rId66" xr:uid="{80FD45D7-C38C-44DB-A53B-5EB167B9BADE}"/>
+    <hyperlink ref="C63" r:id="rId67" xr:uid="{D5A27441-6C5B-4647-B598-FED8A96079BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId68"/>
   <tableParts count="1">
-    <tablePart r:id="rId23"/>
+    <tablePart r:id="rId69"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910F7824-6E14-47CA-8F4A-6A5DD5C58923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588AAC24-31AE-47B2-8D25-0C1DF6A80986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="560">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -980,21 +980,9 @@
     <t>Kostkowanie naprzemienne, Pickslanting</t>
   </si>
   <si>
-    <t>Stosunkowo prosty riff zbudowany w oparciu o ogrywanie power chordów.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bardzo prosty riff dla początkujących, zbudowany w oparciu o ogrywanie w kółko tych trzech power chordów i pustych strun. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Power chord, Ogrywanie akordów, </t>
   </si>
   <si>
-    <t xml:space="preserve">Energetyczny riff łączący ze sobą wiele ciekawych akordów, zagrywek i technik. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szybki riff, zbudowany w oparciu o melodyczne ogrywanie skali. Uwaga, musisz posiadać efekt vibrato. </t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=Qzvr7v1kqcg&amp;t=7s</t>
   </si>
   <si>
@@ -1043,33 +1031,18 @@
     <t>D Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">Dropped C </t>
-  </si>
-  <si>
-    <t>Szybki riff oparty o power chordy i kostkowanie naprzemienne z palm mute.</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1hHYCqi4v8OHqnd1TzLai13yg9xVnIvki&amp;usp=drive_fs</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1MpAiLDmoc0ulWrubjn9qYFiVVewr0zTa&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t xml:space="preserve">Ten riff miesza ze sobą pojedyncze dźwięki z uderzeniami akordów. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Akordy, </t>
   </si>
   <si>
     <t xml:space="preserve">Riff zbudowany na szybkich, pojedynczych dźwiękach kostkowanych w dół, wraz z techniką slide. </t>
   </si>
   <si>
-    <t xml:space="preserve">Głównym elementem tego riffu jest tak zwany legato trill. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten riff przypomina trochę granie fingerstyle. W tym samym momencie musisz grać power chordy oraz wplecioną w tle melodię. Nie zapomnij przestroić gitary do Drop D. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Legendarne intro zbudowane na dwóch dźwiękach w których da się zauważyć harmonię utworu. </t>
   </si>
   <si>
@@ -1082,21 +1055,9 @@
     <t xml:space="preserve">Przygrywka, Rytm, Podciąganie strun, </t>
   </si>
   <si>
-    <t>Ten riff jest zbudowany w oparciu o ogrywanie akordów, ale tak naprawdę grasz dwa dźwięki w melodii, wokół których zmieniają się trzy basy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten riff to po prostu kilka power chordów, które musisz zagrać zgodnie z tabulaturą. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bardzo szybki riff zbudowany w oparciu o tak zwany galop kostkowaniem naprzemiennym. Uwaga na zagrywkę na końcu, która pokonała niejednego gitarzystę. </t>
-  </si>
-  <si>
     <t xml:space="preserve">To bardzo fajnie ułożone akordy w wyższych pozycjach, które należy ograć kostkowaniem. Akordy pochodzą z tak zwanego systemu Caged. </t>
   </si>
   <si>
-    <t xml:space="preserve">Ten riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1ccoFD7pBav79wTMOSp90IJfPt6mylrTs&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1115,123 +1076,30 @@
     <t>https://drive.google.com/open?id=11kwrZ0SeedmPFjIAR_jEHO1sDAN7Ff5G&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>Kiedy Powiem Sobie Dość RIFF A</t>
-  </si>
-  <si>
-    <t>Kiedy Powiem Sobie Dość RIFF B</t>
-  </si>
-  <si>
-    <t>Kocham Cię Kochanie Moje RIFF A</t>
-  </si>
-  <si>
-    <t>Kocham Cię Kochanie Moje RIFF B</t>
-  </si>
-  <si>
-    <t>Nie wierz nigdy kobiecie RIFF A</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło RIFF A</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło RIFF B</t>
-  </si>
-  <si>
-    <t>Nie wierz nigdy kobiecie RIFF B</t>
-  </si>
-  <si>
-    <t>To bardzo szybki riff, łączący ze sobą wiele dodatkowych technik artykulacyjnych. Pamiętaj o przestrojeniu swojej gitary do stroju D Standard.</t>
-  </si>
-  <si>
     <t>Poćwiczysz tutaj technikę staccato, skracając wybrzmiewanie niemal wszystkich dźwięków.</t>
   </si>
   <si>
-    <t>Jest to wyjątkowa aranżacja tego riffu, która bardziej przypomina grę fingerstyle niż jego klasyczną formę. Przypomina trochę „Can’t Stop” zespołu Red Hot Chili Peppers.</t>
-  </si>
-  <si>
-    <t>Jest to riff zagrany za pomocą power chordów, które ze względu na przestrrojenie chwytasz płasko ułożonymi palcami. Działa to trochę jak mini poprzeczki barre.</t>
-  </si>
-  <si>
     <t>To klasyczna przygrywka zagrana w całkiem prosty sposób na pojedynczych dźwiękach.</t>
   </si>
   <si>
-    <t>Ten riff nauczy Cię tłumienia poszczególnych dźwięków za pomocą wypłaszczonych palców, tak aby wybrzmiewały tylko te, które należy grać.</t>
-  </si>
-  <si>
-    <t>To bardzo trudna aranżacja fingerstyle, która łączy ze sobą wszystkie elementy tego riffu.</t>
-  </si>
-  <si>
-    <t>To dosyć prosty riff, który do granych akordów dodaje elementy legato.</t>
-  </si>
-  <si>
-    <t>Idealny riff dla początkujących, który przygotowałem w dwóch pozycjach na gryfie. Wybierz tę, która jest dla Ciebie lepsza.</t>
-  </si>
-  <si>
-    <t>Legendarny riff Nocnego Kochanka, który łączy ze sobą wiele technik artykulacyjnych. Swoją konstrukcją od zawsze przypominał mi „Master of Puppets”.</t>
-  </si>
-  <si>
-    <t>Ten riff łączy ze sobą wiele technik artykulacyjnych, takich jak legato, slide’y, vibrato oraz tłumienie nadgarstkiem.</t>
-  </si>
-  <si>
-    <t>To riff, dzięki któremu popracujesz nad string skippingiem oraz podciąganiem strun, które na początku może przysporzyć wiele problemów.</t>
-  </si>
-  <si>
-    <t>To riff, którego najtrudniejszym elementem jest szybkie przekładanie palca w celu zmiany dźwięków.</t>
-  </si>
-  <si>
     <t>Charakterystyczna linia basowa, która zabrzmi dobrze, jeżeli opanujesz wybrzmiewanie pustych strun tak, aby na siebie nie zachodziły. Całość brzmi trochę w stylu country.</t>
   </si>
   <si>
     <t>Legendarna linia basowa, która jest niemalże idealna dla początkujących gitarzystów.</t>
   </si>
   <si>
-    <t>To jeden z najtrudniejszych riffów, który świetnie nadaje się jako samodzielne ćwiczenie techniki. Skup się na kostkowaniu naprzemiennym oraz zmianie strun za pomocą pochylania płaszczyzny kostkowania.</t>
-  </si>
-  <si>
-    <t>To charakterystyczny bluesowy riff w rytmie shuffle. Można powiedzieć, że jest to Dżemowe podejście do klasyki bluesa.</t>
-  </si>
-  <si>
-    <t>To całkiem prosty riff, ale ma dosyć trudny moment łączący ze sobą techniki legato.</t>
-  </si>
-  <si>
-    <t>Ten riff łączy ze sobą długo wybrzmiewające dźwięki oraz technikę legato.</t>
-  </si>
-  <si>
-    <t>Ten riff mocno opiera się na brzmieniu wynikającym z selektywnego używania techniki tłumienia nadgarstkiem.</t>
-  </si>
-  <si>
-    <t>Świetny riff dla początkujących, dzięki któremu można wyćwiczyć rytmikę.</t>
-  </si>
-  <si>
-    <t>Bardzo prosty riff, który jest idealny dla początkujących.</t>
-  </si>
-  <si>
     <t>Riff, który wykorzystuje dwudźwięki oraz ciekawe współbrzmienia.</t>
   </si>
   <si>
-    <t>To dosyć trudny riff, który przypomina trochę klasyczne kompozycje wykonywane na nylonowych strunach. Jest to must have dla wszystkich fanów zespołu Turbo.</t>
-  </si>
-  <si>
     <t>To klasyczna przygrywka grana na niemalże każdym polskim weselu. Dodatkowo jest to świetny utwór dla początkujących.</t>
   </si>
   <si>
-    <t>Jest to najciężej brzmiący riff zagrany w stroju E Standard. Łączy ze sobą power chordy oraz slide’y.</t>
-  </si>
-  <si>
-    <t>Świetny riff dla początkujących. Wystarczy złapać akord i uderzyć kostką trzymane dźwięki.</t>
-  </si>
-  <si>
     <t>Riff łączący ze sobą umiejętne opalcowanie dźwięków, technikę slide oraz staccato.</t>
   </si>
   <si>
     <t>Klasyka polskiego bluesa, dzięki której nauczysz się pentatoniki, podciągania z odpuszczeniem oraz techniki staccato.</t>
   </si>
   <si>
-    <t>Stosunkowo prosty riff zbudowany w oparciu o kształt power chordów oraz sąsiadujące puste struny. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
-  </si>
-  <si>
-    <t>Bardzo ciekawie brzmiący riff, zbudowany w oparciu o rytm shuffle. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1H_78brL5cpJyEybM9al8QrLgga0DlxRm&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1277,15 +1145,9 @@
     <t>Power chordy, Kostkowanie w dół.</t>
   </si>
   <si>
-    <t>To bardzo melodyjny riff którego granie sprawia wiele radości</t>
-  </si>
-  <si>
     <t>Melodia,</t>
   </si>
   <si>
-    <t>Ten riff polega na graniu dwudźwięków przesuwanych wzdłuż gryfu.</t>
-  </si>
-  <si>
     <t>dwudźwięki,</t>
   </si>
   <si>
@@ -1434,6 +1296,423 @@
   </si>
   <si>
     <t>https://youtu.be/SjtwCo2QJFE</t>
+  </si>
+  <si>
+    <t>Akordy Barre, Slide, Legato, Gitara Akustyczna</t>
+  </si>
+  <si>
+    <t>Przygrywka,</t>
+  </si>
+  <si>
+    <t>Tłumienie, Blues</t>
+  </si>
+  <si>
+    <t>Akordy, Solówka,</t>
+  </si>
+  <si>
+    <t>Wybrzmiewanie</t>
+  </si>
+  <si>
+    <t>Ogrywanie akordów, Wybrzmiewanie, Akordy,</t>
+  </si>
+  <si>
+    <t>To Riff polegający na ogrywaniu akordów zachowując wybrzmiewanie dźwięków.</t>
+  </si>
+  <si>
+    <t>D Standard, Palm mute, Slide, Legato, Harmonie</t>
+  </si>
+  <si>
+    <t>Stosunkowo prosty Riff zbudowany w oparciu o ogrywanie power chordów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo prosty Riff dla początkujących, zbudowany w oparciu o ogrywanie w kółko tych trzech power chordów i pustych strun. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energetyczny Riff łączący ze sobą wiele ciekawych akordów, zagrywek i technik. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybki Riff, zbudowany w oparciu o melodyczne ogrywanie skali. Uwaga, musisz posiadać efekt vibrato. </t>
+  </si>
+  <si>
+    <t>Szybki Riff oparty o power chordy i kostkowanie naprzemienne z palm mute.</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło Riff A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten Riff miesza ze sobą pojedyncze dźwięki z uderzeniami akordów. </t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło Riff B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Głównym elementem tego Riffu jest tak zwany legato trill. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten Riff przypomina trochę granie fingerstyle. W tym samym momencie musisz grać power chordy oraz wplecioną w tle melodię. Nie zapomnij przestroić gitary do Drop D. </t>
+  </si>
+  <si>
+    <t>Ten Riff jest zbudowany w oparciu o ogrywanie akordów, ale tak naprawdę grasz dwa dźwięki w melodii, wokół których zmieniają się trzy basy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten Riff to po prostu kilka power chordów, które musisz zagrać zgodnie z tabulaturą. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo szybki Riff zbudowany w oparciu o tak zwany galop kostkowaniem naprzemiennym. Uwaga na zagrywkę na końcu, która pokonała niejednego gitarzystę. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten Riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
+  </si>
+  <si>
+    <t>To bardzo szybki Riff, łączący ze sobą wiele dodatkowych technik artykulacyjnych. Pamiętaj o przestrojeniu swojej gitary do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>Jest to wyjątkowa aranżacja tego Riffu, która bardziej przypomina grę fingerstyle niż jego klasyczną formę. Przypomina trochę „Can’t Stop” zespołu Red Hot Chili Peppers.</t>
+  </si>
+  <si>
+    <t>Jest to Riff zagrany za pomocą power chordów, które ze względu na przestrrojenie chwytasz płasko ułożonymi palcami. Działa to trochę jak mini poprzeczki barre.</t>
+  </si>
+  <si>
+    <t>Ten Riff nauczy Cię tłumienia poszczególnych dźwięków za pomocą wypłaszczonych palców, tak aby wybrzmiewały tylko te, które należy grać.</t>
+  </si>
+  <si>
+    <t>To bardzo trudna aranżacja fingerstyle, która łączy ze sobą wszystkie elementy tego Riffu.</t>
+  </si>
+  <si>
+    <t>To dosyć prosty Riff, który do granych akordów dodaje elementy legato.</t>
+  </si>
+  <si>
+    <t>Idealny Riff dla początkujących, który przygotowałem w dwóch pozycjach na gryfie. Wybierz tę, która jest dla Ciebie lepsza.</t>
+  </si>
+  <si>
+    <t>Legendarny Riff Nocnego Kochanka, który łączy ze sobą wiele technik artykulacyjnych. Swoją konstrukcją od zawsze przypominał mi „Master of Puppets”.</t>
+  </si>
+  <si>
+    <t>Ten Riff łączy ze sobą wiele technik artykulacyjnych, takich jak legato, slide’y, vibrato oraz tłumienie nadgarstkiem.</t>
+  </si>
+  <si>
+    <t>To Riff, dzięki któremu popracujesz nad string skippingiem oraz podciąganiem strun, które na początku może przysporzyć wiele problemów.</t>
+  </si>
+  <si>
+    <t>To Riff, którego najtrudniejszym elementem jest szybkie przekładanie palca w celu zmiany dźwięków.</t>
+  </si>
+  <si>
+    <t>To jeden z najtrudniejszych Riffów, który świetnie nadaje się jako samodzielne ćwiczenie techniki. Skup się na kostkowaniu naprzemiennym oraz zmianie strun za pomocą pochylania płaszczyzny kostkowania.</t>
+  </si>
+  <si>
+    <t>To charakterystyczny bluesowy Riff w rytmie shuffle. Można powiedzieć, że jest to Dżemowe podejście do klasyki bluesa.</t>
+  </si>
+  <si>
+    <t>To całkiem prosty Riff, ale ma dosyć trudny moment łączący ze sobą techniki legato.</t>
+  </si>
+  <si>
+    <t>Ten Riff łączy ze sobą długo wybrzmiewające dźwięki oraz technikę legato.</t>
+  </si>
+  <si>
+    <t>Ten Riff mocno opiera się na brzmieniu wynikającym z selektywnego używania techniki tłumienia nadgarstkiem.</t>
+  </si>
+  <si>
+    <t>Świetny Riff dla początkujących, dzięki któremu można wyćwiczyć rytmikę.</t>
+  </si>
+  <si>
+    <t>Bardzo prosty Riff, który jest idealny dla początkujących.</t>
+  </si>
+  <si>
+    <t>To dosyć trudny Riff, który przypomina trochę klasyczne kompozycje wykonywane na nylonowych strunach. Jest to must have dla wszystkich fanów zespołu Turbo.</t>
+  </si>
+  <si>
+    <t>Jest to najciężej brzmiący Riff zagrany w stroju E Standard. Łączy ze sobą power chordy oraz slide’y.</t>
+  </si>
+  <si>
+    <t>Świetny Riff dla początkujących. Wystarczy złapać akord i uderzyć kostką trzymane dźwięki.</t>
+  </si>
+  <si>
+    <t>Kiedy Powiem Sobie Dość Riff A</t>
+  </si>
+  <si>
+    <t>Stosunkowo prosty Riff zbudowany w oparciu o kształt power chordów oraz sąsiadujące puste struny. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>Kiedy Powiem Sobie Dość Riff B</t>
+  </si>
+  <si>
+    <t>Bardzo ciekawie brzmiący Riff, zbudowany w oparciu o rytm shuffle. Pamiętaj, aby przestroić gitarę do stroju D Standard.</t>
+  </si>
+  <si>
+    <t>Kocham Cię Kochanie Moje Riff A</t>
+  </si>
+  <si>
+    <t>Kocham Cię Kochanie Moje Riff B</t>
+  </si>
+  <si>
+    <t>Nie wierz nigdy kobiecie Riff A</t>
+  </si>
+  <si>
+    <t>Nie wierz nigdy kobiecie Riff B</t>
+  </si>
+  <si>
+    <t>Ten Riff polega na graniu dwudźwięków przesuwanych wzdłuż gryfu.</t>
+  </si>
+  <si>
+    <t>To bardzo melodyjny Riff którego granie sprawia wiele radości</t>
+  </si>
+  <si>
+    <t>Przygrywka, Rytm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staccato, </t>
+  </si>
+  <si>
+    <t>Przygrywka, Fingerstyle, Tłumienie</t>
+  </si>
+  <si>
+    <t>Power chordy, Dropped D tune down 1/2 step.</t>
+  </si>
+  <si>
+    <t>Drop D, Fingerstyle, Slap, Granie palcami, Wyzwanie</t>
+  </si>
+  <si>
+    <t>Ogrywanie akordów, Wybrzmiewanie, Akordy</t>
+  </si>
+  <si>
+    <t>Akordy, Legato, Solówka, Palm mute,</t>
+  </si>
+  <si>
+    <t>Akordy, Wybrzmiewanie, Staccato, Legato</t>
+  </si>
+  <si>
+    <t>Oktawy, Tłumienie, Kostkowanie w dół,</t>
+  </si>
+  <si>
+    <t>Akordy, Bicie, Legato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tłumienie, Power chordy, Kostkowanie, Legato, Slide, Palm Mute, Tłumienie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melodia, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">String Skipping, Legato, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwudźwięki, Wybrzmiewanie, Slide, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Granie palcami, Slide, Vibrato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie w dół, Akordy, Power chordy, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie, String Skipping, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Kostkowanie w dół, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melodia, Podciąganie strun, Vibrato, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granie palcami, Staccato, Dwudźwięki, Power chordy, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Kostkowanie w dół, Slide, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rake, Tłumienie, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Kostkowanie, </t>
+  </si>
+  <si>
+    <t>Kostkowanie, Kostkowanie naprzemienne, Chromatyka, Pojedyńcza linia,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Fingerstyle, Granie palcami, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwudźwięki, Slide, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Slide, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktawy, Tłumienie, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcza linia, Legato, Slide, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Legato, Slide, Staccato, Wybrzmiewanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Dwudźwięki, Power chordy, Legato, Slide, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solówka, Melodia, Podciąganie strun, Vibrato, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Hybrid Picking, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D Standard, Slide, Puste struny, Dwudźwięki, Vibrato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melodia, Slide, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staccato, Podciąganie strun, Vibrato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rytm, Pojedyńcze dźwięki, Podciąganie strun, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Kostkowanie, Wybrzmiewanie, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Power chordy, Kostkowanie, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Akordy, Ogrywanie akordów, Wybrzmiewanie, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Kostkowanie, </t>
+  </si>
+  <si>
+    <t>Gitara Akustyczna, Dwudźwięki, Staccato, Legato, Slide, Flażolety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropped D tune down 1/2 step, Power chordy, Dwudźwięki, Puste struny, Legato, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Puste struny, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Legato, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie naprzemienne, Pojedyńcze dźwięki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Slide, Shuffle, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podciąganie strun, Melodia, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Power chordy, Ghost Notes, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Power chordy, Pojedyńcze dźwięki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie naprzemienne, Palm Mute, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Dwudźwięki, Ghost Notes, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ghost Notes, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Dwudźwięki, Slide, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramie Tremolo, Wybrzmiewanie, Legato, Slide, Podciąganie strun, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie w dół, Slide, Ogrywanie akordów, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostkowanie, Melodia, Podciąganie strun, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, Dwudźwięki, Wybrzmiewanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, Akordy, Flażolety, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropped C, Dwudźwięki, Power chordy, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwudźwięki, Vibrato, Legato, Slap, Slide, Fingerstyle, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Slide, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy Barre, Slide, Wybrzmiewanie, Ogrywanie akordów, Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, Slide, Wybrzmiewanie, Pojedyńcze dźwięki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Pojedyńcze dźwięki, Palm Mute, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide, Pojedyńcze dźwięki, Legato, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Palm Mute, Chromatyka, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Staccato, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Kostkowanie, Wybrzmiewanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D Standard, Power chordy, Kostkowanie, Legato, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D Standard, Akordy, Ogrywanie akordów, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melodia, Pojedyńcze dźwięki, Slide, Podciąganie strun, Legato, Staccato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Kostkowanie, Slide, Staccato, Chromatyka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, Ogrywanie akordów, Kostkowanie w dół, Wybrzmiewanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Slide, Staccato, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Slide, Kostkowanie, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gitara Akustyczna, Dwudźwięki, Wybrzmiewanie, Slide, Legato, Kostkowanie, Kostkowanie naprzemienne, Hybrid Picking, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwudźwięki, Kostkowanie, Staccato, Legato, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Kostkowanie naprzemienne, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pojedyńcze dźwięki, Slide, Staccato, Kostkowanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, Akordy, Akordy Barre, Palm Mute, Slide, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Pojedyńcze dźwięki, Legato, Tłumienie, </t>
   </si>
 </sst>
 </file>
@@ -2150,7 +2429,7 @@
         <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>401</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2161,7 +2440,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>187</v>
@@ -2170,7 +2449,7 @@
         <v>306</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>315</v>
+        <v>429</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>310</v>
@@ -2184,7 +2463,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>460</v>
+        <v>414</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>186</v>
@@ -2193,10 +2472,10 @@
         <v>308</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2214,10 +2493,10 @@
         <v>305</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>318</v>
+        <v>431</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2235,10 +2514,10 @@
         <v>305</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>319</v>
+        <v>432</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="H5" s="15">
         <v>46205</v>
@@ -2252,7 +2531,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>189</v>
@@ -2261,56 +2540,56 @@
         <v>305</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>337</v>
+        <v>433</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>365</v>
+        <v>434</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>340</v>
+        <v>435</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>366</v>
+        <v>436</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2328,10 +2607,10 @@
         <v>305</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>343</v>
+        <v>437</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2342,7 +2621,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>191</v>
@@ -2351,10 +2630,10 @@
         <v>305</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2365,7 +2644,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>462</v>
+        <v>416</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>192</v>
@@ -2374,10 +2653,10 @@
         <v>306</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2395,10 +2674,10 @@
         <v>305</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2416,10 +2695,10 @@
         <v>305</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2437,10 +2716,10 @@
         <v>308</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2451,7 +2730,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>429</v>
+        <v>383</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>196</v>
@@ -2460,7 +2739,7 @@
         <v>308</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>349</v>
+        <v>439</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>311</v>
@@ -2481,7 +2760,7 @@
         <v>306</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>350</v>
+        <v>440</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>310</v>
@@ -2502,10 +2781,10 @@
         <v>305</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>351</v>
+        <v>441</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2516,7 +2795,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>199</v>
@@ -2525,10 +2804,10 @@
         <v>305</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2539,7 +2818,7 @@
         <v>63</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>200</v>
@@ -2548,9 +2827,11 @@
         <v>307</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>442</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -2560,7 +2841,7 @@
         <v>65</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>201</v>
@@ -2569,10 +2850,10 @@
         <v>307</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2590,9 +2871,11 @@
         <v>306</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="G21" s="5"/>
+        <v>347</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -2609,9 +2892,11 @@
         <v>305</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="G22" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
@@ -2621,7 +2906,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>204</v>
@@ -2630,9 +2915,11 @@
         <v>306</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="G23" s="5"/>
+        <v>445</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -2649,10 +2936,10 @@
         <v>308</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>312</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2663,7 +2950,7 @@
         <v>57</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>206</v>
@@ -2672,9 +2959,11 @@
         <v>305</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>446</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -2684,7 +2973,7 @@
         <v>74</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>445</v>
+        <v>399</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>207</v>
@@ -2693,9 +2982,11 @@
         <v>307</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="G26" s="5"/>
+        <v>447</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
@@ -2712,9 +3003,11 @@
         <v>305</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="G27" s="5"/>
+        <v>448</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -2724,7 +3017,7 @@
         <v>77</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>209</v>
@@ -2733,9 +3026,11 @@
         <v>306</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="G28" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
@@ -2752,28 +3047,32 @@
         <v>305</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>377</v>
+        <v>450</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="6" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>426</v>
+      </c>
       <c r="H30" s="15">
         <v>46224</v>
       </c>
@@ -2786,7 +3085,7 @@
         <v>65</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>211</v>
@@ -2795,10 +3094,10 @@
         <v>305</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>378</v>
+        <v>451</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2816,10 +3115,10 @@
         <v>307</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>379</v>
+        <v>452</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2837,9 +3136,11 @@
         <v>305</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2856,9 +3157,11 @@
         <v>306</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="G34" s="5"/>
+        <v>349</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
@@ -2875,9 +3178,11 @@
         <v>308</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="G35" s="5"/>
+        <v>350</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
@@ -2894,7 +3199,7 @@
         <v>309</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>314</v>
@@ -2915,9 +3220,11 @@
         <v>305</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="G37" s="5"/>
+        <v>455</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
@@ -2934,9 +3241,11 @@
         <v>306</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="G38" s="5"/>
+        <v>456</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
@@ -2953,9 +3262,11 @@
         <v>306</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="G39" s="5"/>
+        <v>457</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
@@ -2972,9 +3283,11 @@
         <v>305</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G40" s="5"/>
+        <v>458</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
@@ -2991,11 +3304,13 @@
         <v>308</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>89</v>
       </c>
@@ -3010,11 +3325,13 @@
         <v>308</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>4</v>
       </c>
@@ -3022,7 +3339,7 @@
         <v>57</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>223</v>
@@ -3031,11 +3348,13 @@
         <v>306</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>90</v>
       </c>
@@ -3043,7 +3362,7 @@
         <v>77</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>224</v>
@@ -3052,11 +3371,13 @@
         <v>307</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>91</v>
       </c>
@@ -3071,9 +3392,11 @@
         <v>308</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="G45" s="5"/>
+        <v>352</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
@@ -3083,7 +3406,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>226</v>
@@ -3092,11 +3415,13 @@
         <v>305</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>2</v>
       </c>
@@ -3111,11 +3436,13 @@
         <v>308</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3123,7 +3450,7 @@
         <v>96</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>228</v>
@@ -3132,11 +3459,13 @@
         <v>306</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>97</v>
       </c>
@@ -3144,7 +3473,7 @@
         <v>98</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>229</v>
@@ -3153,55 +3482,57 @@
         <v>305</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>360</v>
+        <v>464</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>455</v>
+        <v>409</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F50" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>361</v>
+        <v>466</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>305</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>100</v>
       </c>
@@ -3216,43 +3547,49 @@
         <v>305</v>
       </c>
       <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G52" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>362</v>
+        <v>468</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>363</v>
+        <v>469</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="3" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G54" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>102</v>
       </c>
@@ -3267,9 +3604,11 @@
         <v>306</v>
       </c>
       <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G55" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>31</v>
       </c>
@@ -3284,9 +3623,11 @@
         <v>308</v>
       </c>
       <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G56" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>10</v>
       </c>
@@ -3294,7 +3635,7 @@
         <v>42</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>454</v>
+        <v>408</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>233</v>
@@ -3303,9 +3644,11 @@
         <v>305</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>105</v>
       </c>
@@ -3313,7 +3656,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>441</v>
+        <v>395</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>234</v>
@@ -3322,9 +3665,11 @@
         <v>307</v>
       </c>
       <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G58" s="5" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>26</v>
       </c>
@@ -3339,9 +3684,11 @@
         <v>307</v>
       </c>
       <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G59" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>106</v>
       </c>
@@ -3349,7 +3696,7 @@
         <v>41</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>236</v>
@@ -3358,9 +3705,11 @@
         <v>307</v>
       </c>
       <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G60" s="5" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>107</v>
       </c>
@@ -3376,10 +3725,10 @@
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>109</v>
       </c>
@@ -3387,7 +3736,7 @@
         <v>42</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>238</v>
@@ -3396,9 +3745,11 @@
         <v>309</v>
       </c>
       <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G62" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>11</v>
       </c>
@@ -3406,7 +3757,7 @@
         <v>42</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>239</v>
@@ -3415,9 +3766,11 @@
         <v>305</v>
       </c>
       <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G63" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>7</v>
       </c>
@@ -3432,9 +3785,11 @@
         <v>308</v>
       </c>
       <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>12</v>
       </c>
@@ -3442,7 +3797,7 @@
         <v>42</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>241</v>
@@ -3451,9 +3806,11 @@
         <v>305</v>
       </c>
       <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>111</v>
       </c>
@@ -3461,7 +3818,7 @@
         <v>112</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>242</v>
@@ -3470,9 +3827,11 @@
         <v>305</v>
       </c>
       <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G66" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>113</v>
       </c>
@@ -3480,7 +3839,7 @@
         <v>94</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>243</v>
@@ -3489,7 +3848,9 @@
         <v>305</v>
       </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="G67" s="5" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
@@ -3506,9 +3867,11 @@
         <v>309</v>
       </c>
       <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>115</v>
       </c>
@@ -3516,7 +3879,7 @@
         <v>47</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>245</v>
@@ -3525,9 +3888,11 @@
         <v>306</v>
       </c>
       <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>116</v>
       </c>
@@ -3535,7 +3900,7 @@
         <v>117</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>246</v>
@@ -3544,9 +3909,11 @@
         <v>305</v>
       </c>
       <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>118</v>
       </c>
@@ -3561,9 +3928,11 @@
         <v>306</v>
       </c>
       <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G71" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>120</v>
       </c>
@@ -3578,9 +3947,11 @@
         <v>306</v>
       </c>
       <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G72" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>27</v>
       </c>
@@ -3595,9 +3966,11 @@
         <v>306</v>
       </c>
       <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G73" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>122</v>
       </c>
@@ -3612,9 +3985,11 @@
         <v>305</v>
       </c>
       <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G74" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>124</v>
       </c>
@@ -3629,9 +4004,11 @@
         <v>306</v>
       </c>
       <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>125</v>
       </c>
@@ -3639,7 +4016,7 @@
         <v>66</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>252</v>
@@ -3648,43 +4025,49 @@
         <v>306</v>
       </c>
       <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G76" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>364</v>
+        <v>470</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="3" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>309</v>
       </c>
       <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
+      <c r="G77" s="5" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>367</v>
+        <v>471</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="3" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>305</v>
       </c>
       <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>126</v>
       </c>
@@ -3699,9 +4082,11 @@
         <v>306</v>
       </c>
       <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G79" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>28</v>
       </c>
@@ -3716,7 +4101,9 @@
         <v>307</v>
       </c>
       <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
+      <c r="G80" s="5" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
@@ -3733,9 +4120,11 @@
         <v>305</v>
       </c>
       <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G81" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>129</v>
       </c>
@@ -3750,9 +4139,11 @@
         <v>305</v>
       </c>
       <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>29</v>
       </c>
@@ -3760,7 +4151,7 @@
         <v>45</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>257</v>
@@ -3769,9 +4160,11 @@
         <v>308</v>
       </c>
       <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G83" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>130</v>
       </c>
@@ -3786,9 +4179,11 @@
         <v>306</v>
       </c>
       <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G84" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>131</v>
       </c>
@@ -3803,9 +4198,11 @@
         <v>306</v>
       </c>
       <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G85" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>132</v>
       </c>
@@ -3820,9 +4217,11 @@
         <v>306</v>
       </c>
       <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G86" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>134</v>
       </c>
@@ -3837,7 +4236,9 @@
         <v>306</v>
       </c>
       <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
+      <c r="G87" s="5" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
@@ -3847,7 +4248,7 @@
         <v>136</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>449</v>
+        <v>403</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>262</v>
@@ -3856,9 +4257,11 @@
         <v>305</v>
       </c>
       <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G88" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>137</v>
       </c>
@@ -3866,7 +4269,7 @@
         <v>138</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>263</v>
@@ -3875,9 +4278,11 @@
         <v>309</v>
       </c>
       <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G89" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>139</v>
       </c>
@@ -3892,9 +4297,11 @@
         <v>307</v>
       </c>
       <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G90" s="5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>141</v>
       </c>
@@ -3902,7 +4309,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>265</v>
@@ -3911,9 +4318,11 @@
         <v>305</v>
       </c>
       <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>142</v>
       </c>
@@ -3921,7 +4330,7 @@
         <v>143</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>424</v>
+        <v>378</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>266</v>
@@ -3930,9 +4339,11 @@
         <v>305</v>
       </c>
       <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>144</v>
       </c>
@@ -3940,7 +4351,7 @@
         <v>145</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>267</v>
@@ -3949,9 +4360,11 @@
         <v>307</v>
       </c>
       <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>146</v>
       </c>
@@ -3966,9 +4379,11 @@
         <v>306</v>
       </c>
       <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>147</v>
       </c>
@@ -3983,7 +4398,9 @@
         <v>306</v>
       </c>
       <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
+      <c r="G95" s="5" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
@@ -3993,7 +4410,7 @@
         <v>149</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>270</v>
@@ -4002,7 +4419,9 @@
         <v>306</v>
       </c>
       <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="G96" s="5" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
@@ -4019,9 +4438,11 @@
         <v>305</v>
       </c>
       <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G97" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>151</v>
       </c>
@@ -4036,9 +4457,11 @@
         <v>305</v>
       </c>
       <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G98" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>152</v>
       </c>
@@ -4046,7 +4469,7 @@
         <v>153</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>435</v>
+        <v>389</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>273</v>
@@ -4055,9 +4478,11 @@
         <v>305</v>
       </c>
       <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G99" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>154</v>
       </c>
@@ -4065,7 +4490,7 @@
         <v>50</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>274</v>
@@ -4074,9 +4499,11 @@
         <v>308</v>
       </c>
       <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G100" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>13</v>
       </c>
@@ -4091,7 +4518,9 @@
         <v>308</v>
       </c>
       <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
+      <c r="G101" s="5" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -4108,9 +4537,11 @@
         <v>306</v>
       </c>
       <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G102" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>19</v>
       </c>
@@ -4118,7 +4549,7 @@
         <v>156</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>277</v>
@@ -4127,9 +4558,11 @@
         <v>305</v>
       </c>
       <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G103" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>14</v>
       </c>
@@ -4144,9 +4577,11 @@
         <v>307</v>
       </c>
       <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G104" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>157</v>
       </c>
@@ -4161,9 +4596,11 @@
         <v>305</v>
       </c>
       <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G105" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>3</v>
       </c>
@@ -4178,9 +4615,11 @@
         <v>305</v>
       </c>
       <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G106" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>15</v>
       </c>
@@ -4195,7 +4634,9 @@
         <v>306</v>
       </c>
       <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
+      <c r="G107" s="5" t="s">
+        <v>492</v>
+      </c>
       <c r="H107" s="15">
         <v>46195</v>
       </c>
@@ -4208,7 +4649,7 @@
         <v>136</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>282</v>
@@ -4217,9 +4658,11 @@
         <v>308</v>
       </c>
       <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G108" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>159</v>
       </c>
@@ -4227,7 +4670,7 @@
         <v>47</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>283</v>
@@ -4236,9 +4679,11 @@
         <v>306</v>
       </c>
       <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G109" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>160</v>
       </c>
@@ -4253,9 +4698,11 @@
         <v>307</v>
       </c>
       <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G110" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>33</v>
       </c>
@@ -4263,7 +4710,7 @@
         <v>50</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>285</v>
@@ -4272,7 +4719,9 @@
         <v>306</v>
       </c>
       <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
+      <c r="G111" s="5" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
@@ -4289,7 +4738,9 @@
         <v>305</v>
       </c>
       <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
+      <c r="G112" s="5" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
@@ -4299,7 +4750,7 @@
         <v>163</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>437</v>
+        <v>391</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>287</v>
@@ -4308,7 +4759,9 @@
         <v>305</v>
       </c>
       <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
+      <c r="G113" s="5" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
@@ -4325,9 +4778,11 @@
         <v>306</v>
       </c>
       <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G114" s="5" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>5</v>
       </c>
@@ -4335,7 +4790,7 @@
         <v>57</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>444</v>
+        <v>398</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>289</v>
@@ -4344,7 +4799,9 @@
         <v>307</v>
       </c>
       <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
+      <c r="G115" s="5" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
@@ -4361,7 +4818,9 @@
         <v>305</v>
       </c>
       <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
+      <c r="G116" s="5" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
@@ -4378,9 +4837,11 @@
         <v>305</v>
       </c>
       <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G117" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>167</v>
       </c>
@@ -4395,7 +4856,9 @@
         <v>306</v>
       </c>
       <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
+      <c r="G118" s="5" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
@@ -4412,7 +4875,7 @@
         <v>305</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="G119" s="5"/>
     </row>
@@ -4431,7 +4894,7 @@
         <v>305</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="G120" s="5"/>
     </row>
@@ -4443,7 +4906,7 @@
         <v>173</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>295</v>
@@ -4453,7 +4916,7 @@
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5" t="s">
-        <v>419</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -4471,10 +4934,10 @@
         <v>306</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -4492,10 +4955,10 @@
         <v>305</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>414</v>
+        <v>473</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="H123" s="15">
         <v>46206</v>
@@ -4509,7 +4972,7 @@
         <v>42</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>298</v>
@@ -4518,10 +4981,10 @@
         <v>306</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -4532,7 +4995,7 @@
         <v>178</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>299</v>
@@ -4541,10 +5004,10 @@
         <v>306</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>411</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -4562,10 +5025,10 @@
         <v>308</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>408</v>
+        <v>364</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>409</v>
+        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -4576,7 +5039,7 @@
         <v>57</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>426</v>
+        <v>380</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>301</v>
@@ -4585,7 +5048,7 @@
         <v>306</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>407</v>
+        <v>363</v>
       </c>
       <c r="G127" s="5"/>
     </row>
@@ -4597,7 +5060,7 @@
         <v>42</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>302</v>
@@ -4606,7 +5069,7 @@
         <v>309</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>406</v>
+        <v>362</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>313</v>
@@ -4627,7 +5090,7 @@
         <v>306</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="G129" s="5"/>
     </row>
@@ -4646,10 +5109,10 @@
         <v>305</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>403</v>
+        <v>359</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A9E5BE-F7AE-48DF-BF27-40BF19E5C9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE2E218-34D9-438A-A5B9-3B6815BD500C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -1578,9 +1578,6 @@
     <t>https://drive.google.com/open?id=1N28sYCwos6fEu-Zqep7etvVyvZTP92a3&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>To bardzo melodyjny Riff którego granie sprawia wiele radości</t>
-  </si>
-  <si>
     <t>Melodia,</t>
   </si>
   <si>
@@ -1915,6 +1912,9 @@
   </si>
   <si>
     <t>Ogrywanie akordów z biciem i legato. Pilnuj swobodnego pulsu oraz płynnych ozdobników.</t>
+  </si>
+  <si>
+    <t>To bardzo melodyjny Riff którego granie sprawia wiele radości. Zapodaj czyste brzmienie z Kompresorem.</t>
   </si>
 </sst>
 </file>
@@ -2043,6 +2043,40 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2142,40 +2176,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2197,14 +2197,14 @@
     <sortCondition ref="A1:A131"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2717,7 +2717,7 @@
         <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>69</v>
@@ -2882,7 +2882,7 @@
         <v>108</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H20" s="7"/>
     </row>
@@ -2904,7 +2904,7 @@
         <v>113</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H21" s="7"/>
     </row>
@@ -2923,7 +2923,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>117</v>
@@ -2972,7 +2972,7 @@
         <v>126</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H24" s="7"/>
     </row>
@@ -2996,7 +2996,7 @@
         <v>131</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H25" s="7"/>
     </row>
@@ -3039,7 +3039,7 @@
         <v>25</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>140</v>
@@ -3177,7 +3177,7 @@
         <v>25</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>165</v>
@@ -3243,7 +3243,7 @@
         <v>178</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>179</v>
@@ -3607,7 +3607,7 @@
         <v>25</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>255</v>
@@ -3629,7 +3629,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>258</v>
@@ -3651,7 +3651,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>261</v>
@@ -3673,7 +3673,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>265</v>
@@ -3695,7 +3695,7 @@
         <v>19</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>269</v>
@@ -3719,7 +3719,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>273</v>
@@ -3743,7 +3743,7 @@
         <v>101</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>277</v>
@@ -3765,7 +3765,7 @@
         <v>101</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>280</v>
@@ -3789,7 +3789,7 @@
         <v>101</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>284</v>
@@ -3811,7 +3811,7 @@
         <v>12</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>288</v>
@@ -3835,7 +3835,7 @@
         <v>178</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>292</v>
@@ -3859,7 +3859,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>296</v>
@@ -3881,7 +3881,7 @@
         <v>19</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>300</v>
@@ -3905,7 +3905,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>304</v>
@@ -3929,7 +3929,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>309</v>
@@ -3953,7 +3953,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>313</v>
@@ -3975,7 +3975,7 @@
         <v>178</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>316</v>
@@ -3999,7 +3999,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>320</v>
@@ -4023,7 +4023,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>325</v>
@@ -4045,7 +4045,7 @@
         <v>12</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>329</v>
@@ -4067,7 +4067,7 @@
         <v>12</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>333</v>
@@ -4089,7 +4089,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>336</v>
@@ -4111,7 +4111,7 @@
         <v>25</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>340</v>
@@ -4133,7 +4133,7 @@
         <v>12</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>343</v>
@@ -4157,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>347</v>
@@ -4179,7 +4179,7 @@
         <v>178</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>350</v>
@@ -4201,7 +4201,7 @@
         <v>25</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>353</v>
@@ -4223,7 +4223,7 @@
         <v>12</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>356</v>
@@ -4245,7 +4245,7 @@
         <v>101</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>359</v>
@@ -4267,7 +4267,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>363</v>
@@ -4289,7 +4289,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>366</v>
@@ -4313,7 +4313,7 @@
         <v>19</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>370</v>
@@ -4335,7 +4335,7 @@
         <v>12</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>373</v>
@@ -4357,7 +4357,7 @@
         <v>12</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>376</v>
@@ -4379,7 +4379,7 @@
         <v>12</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>380</v>
@@ -4401,7 +4401,7 @@
         <v>12</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>383</v>
@@ -4425,7 +4425,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>388</v>
@@ -4449,7 +4449,7 @@
         <v>178</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>393</v>
@@ -4471,7 +4471,7 @@
         <v>101</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>397</v>
@@ -4495,10 +4495,10 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H91" s="7"/>
     </row>
@@ -4519,7 +4519,7 @@
         <v>25</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>405</v>
@@ -4543,7 +4543,7 @@
         <v>101</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>410</v>
@@ -4565,7 +4565,7 @@
         <v>12</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>413</v>
@@ -4587,7 +4587,7 @@
         <v>12</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G95" s="6" t="s">
         <v>416</v>
@@ -4611,7 +4611,7 @@
         <v>12</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>421</v>
@@ -4633,7 +4633,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>424</v>
@@ -4655,7 +4655,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>427</v>
@@ -4679,10 +4679,10 @@
         <v>25</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H99" s="7"/>
     </row>
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>435</v>
@@ -4725,7 +4725,7 @@
         <v>19</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>435</v>
@@ -4747,7 +4747,7 @@
         <v>12</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>441</v>
@@ -4771,7 +4771,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>445</v>
@@ -4793,7 +4793,7 @@
         <v>101</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>448</v>
@@ -4815,7 +4815,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>451</v>
@@ -4837,7 +4837,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>454</v>
@@ -4859,7 +4859,7 @@
         <v>12</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>457</v>
@@ -4885,7 +4885,7 @@
         <v>19</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>461</v>
@@ -4909,7 +4909,7 @@
         <v>12</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>465</v>
@@ -4931,7 +4931,7 @@
         <v>101</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>469</v>
@@ -4955,7 +4955,7 @@
         <v>12</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>473</v>
@@ -4977,7 +4977,7 @@
         <v>25</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>476</v>
@@ -5001,7 +5001,7 @@
         <v>25</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>481</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>484</v>
@@ -5047,7 +5047,7 @@
         <v>101</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>488</v>
@@ -5069,7 +5069,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>492</v>
@@ -5091,7 +5091,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>492</v>
@@ -5113,7 +5113,7 @@
         <v>12</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>498</v>
@@ -5177,7 +5177,7 @@
         <v>25</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>510</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>515</v>
       </c>
@@ -5221,10 +5221,10 @@
         <v>25</v>
       </c>
       <c r="F123" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="G123" s="6" t="s">
         <v>517</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>518</v>
       </c>
       <c r="H123" s="10">
         <v>46206</v>
@@ -5232,159 +5232,159 @@
     </row>
     <row r="124" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C124" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F124" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="G124" s="6" t="s">
         <v>522</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>523</v>
       </c>
       <c r="H124" s="7"/>
     </row>
     <row r="125" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>527</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="G125" s="6" t="s">
         <v>528</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>529</v>
       </c>
       <c r="H125" s="7"/>
     </row>
     <row r="126" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="G126" s="6" t="s">
         <v>533</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>534</v>
       </c>
       <c r="H126" s="7"/>
     </row>
     <row r="127" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C127" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
     </row>
     <row r="128" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="E128" s="5" t="s">
         <v>178</v>
       </c>
       <c r="F128" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>542</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>543</v>
       </c>
       <c r="H128" s="7"/>
     </row>
     <row r="129" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
     </row>
     <row r="130" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F130" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="G130" s="6" t="s">
         <v>549</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>550</v>
       </c>
       <c r="H130" s="7"/>
     </row>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[W SZPONACH GITARY]\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE2E218-34D9-438A-A5B9-3B6815BD500C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C6C145-32A3-4FFD-A34C-2519790134FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="634">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -1915,6 +1915,18 @@
   </si>
   <si>
     <t>To bardzo melodyjny Riff którego granie sprawia wiele radości. Zapodaj czyste brzmienie z Kompresorem.</t>
+  </si>
+  <si>
+    <t>Kaczor Coś Ty Zrobił</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1RERQpivAWfI5d_I_PGQxwCqldbUd_HAN&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Ten stosunkowo prosty Riff nauczy Cię mieszania akordów z dźwiękami basu granymi Palm Mute.</t>
+  </si>
+  <si>
+    <t>Palm mute, Puste struny, Akordy</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +2005,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2035,6 +2047,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2042,40 +2057,6 @@
     <cellStyle name="Normalny 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2176,6 +2157,40 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2193,18 +2208,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H131" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="A1:H131" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G131">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2405,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -2444,7 +2459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2468,7 +2483,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2492,7 +2507,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -2514,7 +2529,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -2538,7 +2553,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
@@ -2562,7 +2577,7 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -2586,7 +2601,7 @@
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -2610,7 +2625,7 @@
       </c>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -2632,7 +2647,7 @@
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
@@ -2656,7 +2671,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>59</v>
       </c>
@@ -2680,7 +2695,7 @@
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
@@ -2702,7 +2717,7 @@
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -2724,7 +2739,7 @@
       </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
@@ -2746,7 +2761,7 @@
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
@@ -2770,7 +2785,7 @@
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>83</v>
       </c>
@@ -2792,7 +2807,7 @@
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>87</v>
       </c>
@@ -2814,7 +2829,7 @@
       </c>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>92</v>
       </c>
@@ -2838,7 +2853,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>97</v>
       </c>
@@ -2862,7 +2877,7 @@
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>104</v>
       </c>
@@ -2886,7 +2901,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>110</v>
       </c>
@@ -2908,7 +2923,7 @@
       </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>114</v>
       </c>
@@ -2930,7 +2945,7 @@
       </c>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>118</v>
       </c>
@@ -2954,7 +2969,7 @@
       </c>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>123</v>
       </c>
@@ -2976,7 +2991,7 @@
       </c>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>127</v>
       </c>
@@ -3000,7 +3015,7 @@
       </c>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>132</v>
       </c>
@@ -3024,7 +3039,7 @@
       </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>138</v>
       </c>
@@ -3046,7 +3061,7 @@
       </c>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
@@ -3070,7 +3085,7 @@
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>147</v>
       </c>
@@ -3092,7 +3107,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>150</v>
       </c>
@@ -3116,7 +3131,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>155</v>
       </c>
@@ -3140,7 +3155,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>160</v>
       </c>
@@ -3162,7 +3177,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>163</v>
       </c>
@@ -3184,7 +3199,7 @@
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>166</v>
       </c>
@@ -3206,7 +3221,7 @@
       </c>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>171</v>
       </c>
@@ -3228,7 +3243,7 @@
       </c>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>176</v>
       </c>
@@ -3250,7 +3265,7 @@
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>180</v>
       </c>
@@ -3272,7 +3287,7 @@
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>184</v>
       </c>
@@ -3294,7 +3309,7 @@
       </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -3316,7 +3331,7 @@
       </c>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>192</v>
       </c>
@@ -3338,7 +3353,7 @@
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>197</v>
       </c>
@@ -3360,7 +3375,7 @@
       </c>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>201</v>
       </c>
@@ -3382,7 +3397,7 @@
       </c>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>205</v>
       </c>
@@ -3406,7 +3421,7 @@
       </c>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>210</v>
       </c>
@@ -3430,7 +3445,7 @@
       </c>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>215</v>
       </c>
@@ -3452,7 +3467,7 @@
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>220</v>
       </c>
@@ -3476,7 +3491,7 @@
       </c>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>226</v>
       </c>
@@ -3498,1906 +3513,1942 @@
       </c>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>233</v>
+    <row r="48" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="15" t="s">
+        <v>631</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G49" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="H48" s="7"/>
-    </row>
-    <row r="49" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F50" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G50" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H50" s="7"/>
-    </row>
-    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="D51" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="H51" s="7"/>
-    </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>550</v>
+      <c r="F52" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>263</v>
+        <v>111</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F57" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G57" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F58" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G58" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H57" s="7"/>
-    </row>
-    <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+      <c r="H58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D59" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="H58" s="7"/>
-    </row>
-    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>101</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>282</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C60" s="9"/>
       <c r="D60" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F61" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G61" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="H60" s="7"/>
-    </row>
-    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="H61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="4" t="s">
+      <c r="C62" s="9"/>
+      <c r="D62" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F62" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G62" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="H61" s="7"/>
-    </row>
-    <row r="62" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="H62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="H62" s="7"/>
-    </row>
-    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="H63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D64" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E64" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F64" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G64" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="H63" s="7"/>
-    </row>
-    <row r="64" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+      <c r="H64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="4" t="s">
+      <c r="C65" s="9"/>
+      <c r="D65" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F65" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G65" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="H64" s="7"/>
-    </row>
-    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+      <c r="H65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="H65" s="7"/>
-    </row>
-    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>221</v>
+        <v>306</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F67" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G68" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="H67" s="7"/>
-    </row>
-    <row r="68" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+      <c r="H68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="9"/>
-      <c r="D68" s="8" t="s">
+      <c r="C69" s="9"/>
+      <c r="D69" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F69" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G69" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="H68" s="7"/>
-    </row>
-    <row r="69" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="H69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E70" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F70" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G70" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="H69" s="7"/>
-    </row>
-    <row r="70" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="H70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F71" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G71" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="H70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+      <c r="H71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="H71" s="7"/>
-    </row>
-    <row r="72" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>39</v>
+        <v>331</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>601</v>
+        <v>561</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>338</v>
+        <v>39</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>39</v>
+        <v>338</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="H75" s="7"/>
-    </row>
-    <row r="76" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F76" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G77" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H76" s="7"/>
-    </row>
-    <row r="77" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="H77" s="7"/>
-    </row>
-    <row r="78" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>221</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>361</v>
+        <v>39</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>603</v>
+        <v>567</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>66</v>
+        <v>361</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F82" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="H82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G83" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="H82" s="7"/>
-    </row>
-    <row r="83" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+      <c r="H83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D84" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E84" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F84" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="G83" s="6" t="s">
+      <c r="G84" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="H83" s="7"/>
-    </row>
-    <row r="84" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>378</v>
+        <v>39</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F87" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="H87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G88" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="H87" s="7"/>
-    </row>
-    <row r="88" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="H88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F89" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G89" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="H88" s="7"/>
-    </row>
-    <row r="89" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+      <c r="H89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E90" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F90" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="G89" s="6" t="s">
+      <c r="G90" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="H89" s="7"/>
-    </row>
-    <row r="90" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+      <c r="H90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C90" s="9"/>
-      <c r="D90" s="4" t="s">
+      <c r="C91" s="9"/>
+      <c r="D91" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E91" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F91" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G91" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="H90" s="7"/>
-    </row>
-    <row r="91" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D92" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="H91" s="7"/>
-    </row>
-    <row r="92" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F92" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="H92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="G93" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="H92" s="7"/>
-    </row>
-    <row r="93" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
+      <c r="H93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C94" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D94" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E94" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F94" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="G94" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="H93" s="7"/>
-    </row>
-    <row r="94" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
+      <c r="H94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C94" s="9"/>
-      <c r="D94" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="H94" s="7"/>
-    </row>
-    <row r="95" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>419</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C96" s="9"/>
       <c r="D96" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F96" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="H96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="G97" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="H96" s="7"/>
-    </row>
-    <row r="97" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="H97" s="7"/>
-    </row>
-    <row r="98" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="4" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>575</v>
+        <v>613</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>430</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C99" s="9"/>
       <c r="D99" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F99" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G100" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="H99" s="7"/>
-    </row>
-    <row r="100" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="H100" s="7"/>
+    </row>
+    <row r="101" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C101" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="H100" s="7"/>
-    </row>
-    <row r="101" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="9"/>
-      <c r="D101" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>577</v>
+        <v>615</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>435</v>
       </c>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>439</v>
+        <v>23</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H102" s="7"/>
+    </row>
+    <row r="103" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C103" s="9"/>
+      <c r="D103" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E103" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F103" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G103" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="H102" s="7"/>
-    </row>
-    <row r="103" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+      <c r="H103" s="7"/>
+    </row>
+    <row r="104" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B104" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D104" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E104" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F103" s="6" t="s">
+      <c r="F104" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="G103" s="6" t="s">
+      <c r="G104" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="H103" s="7"/>
-    </row>
-    <row r="104" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+      <c r="H104" s="7"/>
+    </row>
+    <row r="105" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" s="9"/>
-      <c r="D104" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>619</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="H104" s="7"/>
-    </row>
-    <row r="105" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="H105" s="7"/>
+    </row>
+    <row r="106" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="H105" s="7"/>
-    </row>
-    <row r="106" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C106" s="9"/>
-      <c r="D106" s="8" t="s">
-        <v>453</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F106" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H106" s="7"/>
+    </row>
+    <row r="107" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="9"/>
+      <c r="D107" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G107" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="H106" s="7"/>
-    </row>
-    <row r="107" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+      <c r="H107" s="7"/>
+    </row>
+    <row r="108" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C107" s="9"/>
-      <c r="D107" s="4" t="s">
+      <c r="C108" s="9"/>
+      <c r="D108" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E108" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F108" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G108" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="H107" s="10">
+      <c r="H108" s="10">
         <v>46195</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D109" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E109" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F109" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G109" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="H108" s="7"/>
-    </row>
-    <row r="109" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="H109" s="7"/>
+    </row>
+    <row r="110" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B110" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D110" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E110" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F110" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G110" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="H109" s="7"/>
-    </row>
-    <row r="110" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+      <c r="H110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C110" s="9"/>
-      <c r="D110" s="4" t="s">
+      <c r="C111" s="9"/>
+      <c r="D111" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E111" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F111" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G111" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="H110" s="7"/>
-    </row>
-    <row r="111" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+      <c r="H111" s="7"/>
+    </row>
+    <row r="112" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C112" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E112" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F112" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="G111" s="6" t="s">
+      <c r="G112" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="H111" s="7"/>
-    </row>
-    <row r="112" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+      <c r="H112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="9"/>
-      <c r="D112" s="4" t="s">
+      <c r="C113" s="9"/>
+      <c r="D113" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>625</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="H112" s="7"/>
-    </row>
-    <row r="113" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F113" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="H113" s="7"/>
+    </row>
+    <row r="114" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="G114" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="H113" s="7"/>
-    </row>
-    <row r="114" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+      <c r="H114" s="7"/>
+    </row>
+    <row r="115" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="9"/>
-      <c r="D114" s="4" t="s">
+      <c r="C115" s="9"/>
+      <c r="D115" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E115" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F115" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="G115" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="H114" s="7"/>
-    </row>
-    <row r="115" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+      <c r="H115" s="7"/>
+    </row>
+    <row r="116" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E116" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F115" s="6" t="s">
+      <c r="F116" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="G115" s="6" t="s">
+      <c r="G116" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="H115" s="7"/>
-    </row>
-    <row r="116" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="H116" s="7"/>
+    </row>
+    <row r="117" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C116" s="9"/>
-      <c r="D116" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="H116" s="7"/>
-    </row>
-    <row r="117" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>628</v>
+        <v>580</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>492</v>
       </c>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>496</v>
+        <v>128</v>
       </c>
       <c r="C118" s="9"/>
       <c r="D118" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>128</v>
+        <v>496</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="G119" s="6"/>
+        <v>581</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>498</v>
+      </c>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>503</v>
+        <v>128</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>508</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="C121" s="9"/>
       <c r="D121" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>510</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C122" s="9"/>
+      <c r="C122" s="8" t="s">
+        <v>508</v>
+      </c>
       <c r="D122" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>513</v>
+        <v>582</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="H123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C124" s="9"/>
+      <c r="D124" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E124" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F124" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="G124" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H124" s="10">
         <v>46206</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+    <row r="125" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B125" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D125" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="H124" s="7"/>
-    </row>
-    <row r="125" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>526</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="H125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G126" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="H125" s="7"/>
-    </row>
-    <row r="126" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+      <c r="H126" s="7"/>
+    </row>
+    <row r="127" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C126" s="9"/>
-      <c r="D126" s="4" t="s">
+      <c r="C127" s="9"/>
+      <c r="D127" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E127" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F127" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G127" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="H126" s="7"/>
-    </row>
-    <row r="127" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
+      <c r="H127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D128" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F128" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="G127" s="6"/>
-      <c r="H127" s="7"/>
-    </row>
-    <row r="128" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+      <c r="G128" s="6"/>
+      <c r="H128" s="7"/>
+    </row>
+    <row r="129" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="H128" s="7"/>
-    </row>
-    <row r="129" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C129" s="9"/>
+      <c r="C129" s="3" t="s">
+        <v>539</v>
+      </c>
       <c r="D129" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="G129" s="6"/>
+        <v>541</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>542</v>
+      </c>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="G130" s="6"/>
+      <c r="H130" s="7"/>
+    </row>
+    <row r="131" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="E131" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F131" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="G131" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="H130" s="7"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
       <c r="H131" s="7"/>
     </row>
+    <row r="132" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -5431,46 +5482,47 @@
     <hyperlink ref="C44" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
     <hyperlink ref="D44" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="C46" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C48" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D50" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D51" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C57" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C58" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C60" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C62" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C63" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C65" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C66" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C67" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C69" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C70" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C76" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C83" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C88" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C89" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C91" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C92" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C93" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C96" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C99" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C100" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C103" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C108" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C109" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C111" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C113" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C115" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C121" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C124" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C125" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C127" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C128" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C49" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C51" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="D51" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="D52" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C58" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C59" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C61" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C63" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C64" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C66" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C67" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C68" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C70" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C71" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C77" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C84" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C89" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C90" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C92" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C93" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C94" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C97" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C100" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C101" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C104" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C109" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C110" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C112" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C114" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C116" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C122" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C125" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C126" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C128" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C129" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D48" r:id="rId68" xr:uid="{66F040CE-FF3D-46CB-9703-FEC90705A151}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId68"/>
+    <tablePart r:id="rId69"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C6C145-32A3-4FFD-A34C-2519790134FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034F6C86-3DCC-4C50-B1E8-344E2D3DB071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="638">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -1927,13 +1927,25 @@
   </si>
   <si>
     <t>Palm mute, Puste struny, Akordy</t>
+  </si>
+  <si>
+    <t>Nieudany skok</t>
+  </si>
+  <si>
+    <t>Legato, Akordy, Dead notes</t>
+  </si>
+  <si>
+    <t>Riff oparto o mieszanie akordów z legatem i wytłumionymi dźwiękami.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Pec27tddCPd2YbnD8OKBsYoONHkjAJCi&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1967,6 +1979,13 @@
       <sz val="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1976,7 +1995,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1999,13 +2018,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2049,6 +2081,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2206,8 +2250,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H131" totalsRowShown="0" dataDxfId="8">
-  <autoFilter ref="A1:H131" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H132" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="A1:H132" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -3533,7 +3577,9 @@
       <c r="G48" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="H48" s="7"/>
+      <c r="H48" s="10">
+        <v>46252</v>
+      </c>
     </row>
     <row r="49" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
@@ -5425,7 +5471,30 @@
       </c>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="B132" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C132" s="17"/>
+      <c r="D132" s="18" t="s">
+        <v>637</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="G132" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="H132" s="19">
+        <v>46252</v>
+      </c>
+    </row>
     <row r="133" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="135" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA52D818-C34F-4B15-9E0F-A5F58CA9416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA95D3B1-08D4-4D95-9AA4-4F809CFC0700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="0" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="654">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -1975,6 +1975,18 @@
   </si>
   <si>
     <t>Melodia, Pentatonika</t>
+  </si>
+  <si>
+    <t>Jak igła</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1oJji1ll8Tqp7URnxj4uCHdLo7zvZ8jAG&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Ten Riff jest grany w oparciu o ogrywanie akordów z dodatkowymi dźwiękami</t>
+  </si>
+  <si>
+    <t>Akordy, Ogrywanie akordów, Let ring</t>
   </si>
 </sst>
 </file>
@@ -2106,24 +2118,6 @@
     <cellStyle name="Normalny 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -2317,6 +2311,24 @@
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2331,20 +2343,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H135" totalsRowShown="0" headerRowDxfId="0" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H135" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H135" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="WYKONAWCA" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="YT" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Link do dysku" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Poziom" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Opis" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tagi" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DATA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5634,14 +5646,28 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="9"/>
-      <c r="B135" s="9"/>
+      <c r="A135" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="C135" s="3"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="4"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
+      <c r="D135" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="H135" s="12">
+        <v>46253</v>
+      </c>
     </row>
     <row r="136" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="137" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA95D3B1-08D4-4D95-9AA4-4F809CFC0700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463B704B-9341-4586-9402-078D5048FED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="658">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -1987,6 +1987,18 @@
   </si>
   <si>
     <t>Akordy, Ogrywanie akordów, Let ring</t>
+  </si>
+  <si>
+    <t>Wenus, Mars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzięki temu Riffowi nauczysz się grać dźwięki z ich nieprzerwanym wybrzmiewaniem. </t>
+  </si>
+  <si>
+    <t>Akordy, Wybrzmiewanie</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1NqDroG2Ny6Ce9iaZd67gP_5SYdKraQ34&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2055,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2066,13 +2078,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2111,6 +2158,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2343,8 +2408,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H135" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H135" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H136" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H136" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -5669,7 +5734,30 @@
         <v>46253</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" s="16"/>
+      <c r="D136" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E136" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="G136" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="H136" s="19">
+        <v>46253</v>
+      </c>
+    </row>
     <row r="137" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463B704B-9341-4586-9402-078D5048FED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02CA46D-708F-466A-B1AF-5581843AA931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="662">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -1999,6 +1999,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1NqDroG2Ny6Ce9iaZd67gP_5SYdKraQ34&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Bujanie w Obłokach</t>
+  </si>
+  <si>
+    <t>Ten Riff nauczy Cię ogrywać akordy wraz z całą masą dołączonych dźwięków melodycznych. Całość utrudnia nam jeszcze szybkie tempo 168 BPM.</t>
+  </si>
+  <si>
+    <t>Ogrywanie akordów, Legato, Akordy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1gCOuV-YiUj2Wcz3hSX4g1aGHWojclW3D&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -2119,7 +2131,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2174,6 +2186,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2408,8 +2423,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H136" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H136" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H137" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H137" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -5758,7 +5773,30 @@
         <v>46253</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="14" t="s">
+        <v>658</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C137" s="16"/>
+      <c r="D137" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="E137" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F137" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="G137" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="H137" s="19">
+        <v>46254</v>
+      </c>
+    </row>
     <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5848,10 +5886,11 @@
     <hyperlink ref="C129" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
     <hyperlink ref="D48" r:id="rId68" xr:uid="{66F040CE-FF3D-46CB-9703-FEC90705A151}"/>
     <hyperlink ref="D133" r:id="rId69" xr:uid="{00370498-EC18-4332-B7F3-88DF915181F2}"/>
+    <hyperlink ref="D137" r:id="rId70" xr:uid="{064732EC-117E-48C1-96EC-90F001DF425E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId70"/>
+    <tablePart r:id="rId71"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02CA46D-708F-466A-B1AF-5581843AA931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA99E9EE-5678-4D95-9513-114B41BC81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="666">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -2011,6 +2011,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1gCOuV-YiUj2Wcz3hSX4g1aGHWojclW3D&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Memu miastu na do widzenia</t>
+  </si>
+  <si>
+    <t>Shuffle, Kostkowanie naprzemienne, Legato</t>
+  </si>
+  <si>
+    <t>Riff w Triolowym rytmie Shuffle pomoże Ci ogarnąć legato oraz triolowe kostkowanie naprzemienne. Jest pełen dramaturgii oraz ciekawych zagrywek.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1XLwA3TWYdima7Fv_FgE_PfRaxZMveHCy&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -2423,8 +2435,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H137" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H137" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H138" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H138" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -5797,7 +5809,30 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="s">
+        <v>662</v>
+      </c>
+      <c r="B138" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C138" s="16"/>
+      <c r="D138" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="E138" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F138" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="G138" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="H138" s="19">
+        <v>46254</v>
+      </c>
+    </row>
     <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="141" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA99E9EE-5678-4D95-9513-114B41BC81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5B601-7C1C-4D8C-A6FB-8F730D9FEE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="670">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -2023,6 +2023,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1XLwA3TWYdima7Fv_FgE_PfRaxZMveHCy&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Nie mam nic, prócz ciebie</t>
+  </si>
+  <si>
+    <t>Riff zbudowany w oparciu o tzw. Spread Triads, na pewno nauczy Cię sprawnie zmieniać struny.</t>
+  </si>
+  <si>
+    <t>Akordy, Ogrywanie akordów</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Cvo-tE93dbs1c2-mnPBrsu349MJduHQI&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -2435,8 +2447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H138" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H138" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H139" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H139" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -5833,23 +5845,46 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="B139" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" s="16"/>
+      <c r="D139" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="E139" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="G139" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="H139" s="19">
+        <v>46254</v>
+      </c>
+    </row>
     <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="141" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="142" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="144" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -5922,10 +5957,11 @@
     <hyperlink ref="D48" r:id="rId68" xr:uid="{66F040CE-FF3D-46CB-9703-FEC90705A151}"/>
     <hyperlink ref="D133" r:id="rId69" xr:uid="{00370498-EC18-4332-B7F3-88DF915181F2}"/>
     <hyperlink ref="D137" r:id="rId70" xr:uid="{064732EC-117E-48C1-96EC-90F001DF425E}"/>
+    <hyperlink ref="D139" r:id="rId71" xr:uid="{E988686F-B443-474B-9F94-4F7BC7B81D47}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId71"/>
+    <tablePart r:id="rId72"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5B601-7C1C-4D8C-A6FB-8F730D9FEE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB917888-6019-491E-914E-4D507E93F2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18990" yWindow="-105" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="675">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -2035,6 +2035,21 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1Cvo-tE93dbs1c2-mnPBrsu349MJduHQI&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ThTbX9dW6jVa5_AbNoa79kTk3z3uh6vV&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Niepisane</t>
+  </si>
+  <si>
+    <t>Bracia</t>
+  </si>
+  <si>
+    <t>Ogrywanie akordów, dead notes, slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten z pozoru prosty riff zawiera w sobie wyzwanie w postaci ciekawego opalcowania dźwięków zapisanych w tabulaturze. </t>
   </si>
 </sst>
 </file>
@@ -2447,8 +2462,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H139" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H139" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H140" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H140" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H131">
     <sortCondition ref="A1:A131"/>
   </sortState>
@@ -5869,7 +5884,30 @@
         <v>46254</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="C140" s="16"/>
+      <c r="D140" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="E140" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="G140" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="H140" s="19">
+        <v>46254</v>
+      </c>
+    </row>
     <row r="141" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="142" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/KONSPEKT - NPR.xlsx
+++ b/KONSPEKT - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB917888-6019-491E-914E-4D507E93F2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64802CFF-D3BC-4B92-8F71-63824BBE7572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18990" yWindow="-105" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
